--- a/results/consolidated/NF_vs_Standard_GARCH_Comparison.xlsx
+++ b/results/consolidated/NF_vs_Standard_GARCH_Comparison.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Overall mean MSE - NF-GARCH</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0291487681832248</t>
+    <t xml:space="preserve">0.000433198859237968</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean AIC - Standard</t>
@@ -54,13 +54,13 @@
     <t xml:space="preserve">Overall mean AIC - NF-GARCH</t>
   </si>
   <si>
-    <t xml:space="preserve">-23528.7963263558</t>
+    <t xml:space="preserve">-25835.7365290827</t>
   </si>
   <si>
     <t xml:space="preserve">NF-GARCH wins (lower MSE)</t>
   </si>
   <si>
-    <t xml:space="preserve">7</t>
+    <t xml:space="preserve">6</t>
   </si>
   <si>
     <t xml:space="preserve">Standard GARCH wins (lower MSE)</t>
@@ -728,13 +728,13 @@
         <v>-25451.6514751415</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000352619357668561</v>
+        <v>0.000353285522699968</v>
       </c>
       <c r="H2" t="n">
         <v>0.000559673107021087</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0112793660229891</v>
+        <v>0.0112661449369954</v>
       </c>
       <c r="J2" t="n">
         <v>0.0137454998374633</v>
@@ -749,10 +749,10 @@
         <v>-0.00000000000363797880709171</v>
       </c>
       <c r="N2" t="n">
-        <v>36.9954794602493</v>
+        <v>36.876451938103</v>
       </c>
       <c r="O2" t="n">
-        <v>17.9413905906338</v>
+        <v>18.037575423125</v>
       </c>
     </row>
     <row r="3">
@@ -762,45 +762,29 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
-        <v>31837.7685390903</v>
-      </c>
+      <c r="C3"/>
       <c r="D3" t="n">
         <v>31837.7685390903</v>
       </c>
-      <c r="E3" t="n">
-        <v>31876.2595018854</v>
-      </c>
+      <c r="E3"/>
       <c r="F3" t="n">
         <v>31876.2595018854</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.718525068301419</v>
-      </c>
+      <c r="G3"/>
       <c r="H3" t="n">
         <v>66.5223139166787</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.0920867446967219</v>
-      </c>
+      <c r="I3"/>
       <c r="J3" t="n">
         <v>1.54717433862132</v>
       </c>
-      <c r="K3" t="n">
-        <v>-15912.8842695452</v>
-      </c>
+      <c r="K3"/>
       <c r="L3" t="n">
         <v>-15912.8842695452</v>
       </c>
-      <c r="M3" t="n">
-        <v>0.00000000000727595761418343</v>
-      </c>
-      <c r="N3" t="n">
-        <v>98.9198736093254</v>
-      </c>
-      <c r="O3" t="n">
-        <v>94.048069283596</v>
-      </c>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -822,13 +806,13 @@
         <v>-27435.5740553771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000411248257046973</v>
+        <v>0.00041244704938497</v>
       </c>
       <c r="H4" t="n">
         <v>0.000597494046328344</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0128229550886813</v>
+        <v>0.0128394160282186</v>
       </c>
       <c r="J4" t="n">
         <v>0.0145061145911386</v>
@@ -843,10 +827,10 @@
         <v>-0.00000000000727595761418343</v>
       </c>
       <c r="N4" t="n">
-        <v>31.1711539932269</v>
+        <v>30.9705172931019</v>
       </c>
       <c r="O4" t="n">
-        <v>11.60310358699</v>
+        <v>11.4896277183561</v>
       </c>
     </row>
     <row r="5">
@@ -865,11 +849,11 @@
       </c>
       <c r="F5"/>
       <c r="G5" t="n">
-        <v>0.000467577549242258</v>
+        <v>0.000483531432433468</v>
       </c>
       <c r="H5"/>
       <c r="I5" t="n">
-        <v>0.0135244910484579</v>
+        <v>0.0135945586851025</v>
       </c>
       <c r="J5"/>
       <c r="K5" t="n">
@@ -944,16 +928,16 @@
         <v>42</v>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>-23528.7963263558</v>
+        <v>-25835.7365290827</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0291487681832248</v>
+        <v>0.000433198859237968</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0159597825579296</v>
+        <v>0.0128236695838548</v>
       </c>
     </row>
     <row r="3">
@@ -1014,21 +998,21 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" t="n">
         <v>6</v>
@@ -1037,20 +1021,6 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>33.3333333333333</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="n">
         <v>33.3333333333333</v>
       </c>
     </row>
@@ -1725,10 +1695,10 @@
         <v>15436.5575706349</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0000471221203664775</v>
+        <v>0.0000429924605098405</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00506340397644398</v>
+        <v>0.00490017529074978</v>
       </c>
       <c r="I21" t="s">
         <v>42</v>
@@ -1757,10 +1727,10 @@
         <v>15536.6553205405</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0000541902060297839</v>
+        <v>0.0000520595129536844</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00534488120657274</v>
+        <v>0.00528619064757042</v>
       </c>
       <c r="I22" t="s">
         <v>42</v>
@@ -1789,10 +1759,10 @@
         <v>12835.4618918238</v>
       </c>
       <c r="G23" t="n">
-        <v>0.000151102849544144</v>
+        <v>0.000153700150191844</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0093812057061357</v>
+        <v>0.00936764893306355</v>
       </c>
       <c r="I23" t="s">
         <v>42</v>
@@ -1821,10 +1791,10 @@
         <v>8150.29805814787</v>
       </c>
       <c r="G24" t="n">
-        <v>0.00134506210144947</v>
+        <v>0.00142634329904931</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0267916397053963</v>
+        <v>0.0272432424628154</v>
       </c>
       <c r="I24" t="s">
         <v>42</v>
@@ -1853,10 +1823,10 @@
         <v>10907.308175535</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000413129750487411</v>
+        <v>0.000409421267002899</v>
       </c>
       <c r="H25" t="n">
-        <v>0.014402843653106</v>
+        <v>0.0144130890260051</v>
       </c>
       <c r="I25" t="s">
         <v>42</v>
@@ -1885,10 +1855,10 @@
         <v>8785.54444202782</v>
       </c>
       <c r="G26" t="n">
-        <v>0.000852662289321726</v>
+        <v>0.000871937248769845</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0211827623315875</v>
+        <v>0.0212944310569644</v>
       </c>
       <c r="I26" t="s">
         <v>42</v>
@@ -1917,10 +1887,10 @@
         <v>16686.4152954809</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0000468960991281148</v>
+        <v>0.000042881880258254</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00503851779434072</v>
+        <v>0.00488461971956549</v>
       </c>
       <c r="I27" t="s">
         <v>42</v>
@@ -1949,10 +1919,10 @@
         <v>16558.6700118246</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0000541989383920334</v>
+        <v>0.000052058658312496</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0053442522767311</v>
+        <v>0.0052840979932641</v>
       </c>
       <c r="I28" t="s">
         <v>42</v>
@@ -1981,10 +1951,10 @@
         <v>13796.2027317123</v>
       </c>
       <c r="G29" t="n">
-        <v>0.00015096287634305</v>
+        <v>0.000153260125523895</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00934033768264938</v>
+        <v>0.00932006142463944</v>
       </c>
       <c r="I29" t="s">
         <v>42</v>
@@ -2013,10 +1983,10 @@
         <v>9453.10713795071</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00130997725605224</v>
+        <v>0.00139596012545205</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0263696420670088</v>
+        <v>0.0269213319681704</v>
       </c>
       <c r="I30" t="s">
         <v>42</v>
@@ -2045,10 +2015,10 @@
         <v>12251.0385138578</v>
       </c>
       <c r="G31" t="n">
-        <v>0.000412427477910599</v>
+        <v>0.000408453415032372</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0143943179341497</v>
+        <v>0.0143806332568695</v>
       </c>
       <c r="I31" t="s">
         <v>42</v>
@@ -2077,10 +2047,10 @@
         <v>10792.9568311302</v>
       </c>
       <c r="G32" t="n">
-        <v>0.000773198625882046</v>
+        <v>0.000793309046145127</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0196400882473723</v>
+        <v>0.019839182441553</v>
       </c>
       <c r="I32" t="s">
         <v>42</v>
@@ -2109,10 +2079,10 @@
         <v>17297.2571301008</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0000400626614373225</v>
+        <v>0.0000389270752310303</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00470925312283025</v>
+        <v>0.004634694296471</v>
       </c>
       <c r="I33" t="s">
         <v>42</v>
@@ -2141,10 +2111,10 @@
         <v>17068.3741774856</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0000515527973425671</v>
+        <v>0.0000511182550312698</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00525776264751765</v>
+        <v>0.0053035667901323</v>
       </c>
       <c r="I34" t="s">
         <v>42</v>
@@ -2173,10 +2143,10 @@
         <v>14349.7081110585</v>
       </c>
       <c r="G35" t="n">
-        <v>0.000188423406765555</v>
+        <v>0.000179474887527678</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0105524299703285</v>
+        <v>0.0104374757850525</v>
       </c>
       <c r="I35" t="s">
         <v>42</v>
@@ -2205,10 +2175,10 @@
         <v>9910.00882021353</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00111959510690415</v>
+        <v>0.00113138411916276</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0241058175385153</v>
+        <v>0.0242058272469228</v>
       </c>
       <c r="I36" t="s">
         <v>42</v>
@@ -2237,10 +2207,10 @@
         <v>12626.8050283989</v>
       </c>
       <c r="G37" t="n">
-        <v>0.000372757634185981</v>
+        <v>0.000372110242411962</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0138921120121489</v>
+        <v>0.0137892412456215</v>
       </c>
       <c r="I37" t="s">
         <v>42</v>
@@ -2269,10 +2239,10 @@
         <v>11206.0417872593</v>
       </c>
       <c r="G38" t="n">
-        <v>0.000695097935646265</v>
+        <v>0.000701667716945119</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0184203552407474</v>
+        <v>0.0186656908051118</v>
       </c>
       <c r="I38" t="s">
         <v>42</v>
@@ -2283,34 +2253,34 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
         <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D39" t="n">
-        <v>31837.7685390903</v>
+        <v>-32326.2491294199</v>
       </c>
       <c r="E39" t="n">
-        <v>31876.2595018854</v>
+        <v>-32287.7581666248</v>
       </c>
       <c r="F39" t="n">
-        <v>-15912.8842695452</v>
+        <v>16169.12456471</v>
       </c>
       <c r="G39" t="n">
-        <v>0.718525068301419</v>
+        <v>0.0000344213950678341</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0920867446967219</v>
+        <v>0.00423485074942777</v>
       </c>
       <c r="I39" t="s">
         <v>42</v>
       </c>
       <c r="J39" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40">
@@ -2321,22 +2291,22 @@
         <v>55</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D40" t="n">
-        <v>-32326.2491294199</v>
+        <v>-31954.3769009613</v>
       </c>
       <c r="E40" t="n">
-        <v>-32287.7581666248</v>
+        <v>-31915.8859381662</v>
       </c>
       <c r="F40" t="n">
-        <v>16169.12456471</v>
+        <v>15983.1884504807</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0000344245658589725</v>
+        <v>0.000040961652767101</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00423507712086083</v>
+        <v>0.00452963118836436</v>
       </c>
       <c r="I40" t="s">
         <v>42</v>
@@ -2353,22 +2323,22 @@
         <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D41" t="n">
-        <v>-31954.3769009613</v>
+        <v>-26765.1554633125</v>
       </c>
       <c r="E41" t="n">
-        <v>-31915.8859381662</v>
+        <v>-26726.6645005174</v>
       </c>
       <c r="F41" t="n">
-        <v>15983.1884504807</v>
+        <v>13388.5777316562</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0000409777544596631</v>
+        <v>0.000117589911688175</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0045298303922697</v>
+        <v>0.00815181462650758</v>
       </c>
       <c r="I41" t="s">
         <v>42</v>
@@ -2385,28 +2355,28 @@
         <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D42" t="n">
-        <v>-26765.1554633125</v>
+        <v>-17940.7188127727</v>
       </c>
       <c r="E42" t="n">
-        <v>-26726.6645005174</v>
+        <v>-17902.2278499776</v>
       </c>
       <c r="F42" t="n">
-        <v>13388.5777316562</v>
+        <v>8976.35940638635</v>
       </c>
       <c r="G42" t="n">
-        <v>0.00011769745293201</v>
+        <v>0.00101199956331745</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00815489849998383</v>
+        <v>0.0221733143992038</v>
       </c>
       <c r="I42" t="s">
         <v>42</v>
       </c>
       <c r="J42" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43">
@@ -2417,22 +2387,22 @@
         <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D43" t="n">
-        <v>-17940.7188127727</v>
+        <v>-23433.1284200857</v>
       </c>
       <c r="E43" t="n">
-        <v>-17902.2278499776</v>
+        <v>-23394.6374572906</v>
       </c>
       <c r="F43" t="n">
-        <v>8976.35940638635</v>
+        <v>11722.5642100428</v>
       </c>
       <c r="G43" t="n">
-        <v>0.00100380132812952</v>
+        <v>0.00031699205138684</v>
       </c>
       <c r="H43" t="n">
-        <v>0.022140732321569</v>
+        <v>0.0121101815907052</v>
       </c>
       <c r="I43" t="s">
         <v>42</v>
@@ -2449,59 +2419,27 @@
         <v>55</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D44" t="n">
-        <v>-23433.1284200857</v>
+        <v>-20521.2259010673</v>
       </c>
       <c r="E44" t="n">
-        <v>-23394.6374572906</v>
+        <v>-20482.7349382722</v>
       </c>
       <c r="F44" t="n">
-        <v>11722.5642100428</v>
+        <v>10266.6129505337</v>
       </c>
       <c r="G44" t="n">
-        <v>0.000319284269996263</v>
+        <v>0.000597748561972406</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0121920750030135</v>
+        <v>0.0163970770677635</v>
       </c>
       <c r="I44" t="s">
         <v>42</v>
       </c>
       <c r="J44" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>33</v>
-      </c>
-      <c r="B45" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" t="s">
-        <v>59</v>
-      </c>
-      <c r="D45" t="n">
-        <v>-20521.2259010673</v>
-      </c>
-      <c r="E45" t="n">
-        <v>-20482.7349382722</v>
-      </c>
-      <c r="F45" t="n">
-        <v>10266.6129505337</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0.00059953077463494</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.0164235828002378</v>
-      </c>
-      <c r="I45" t="s">
-        <v>42</v>
-      </c>
-      <c r="J45" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2647,22 +2585,22 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0559801225270784</v>
+        <v>0.000786443888054012</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000773198625882046</v>
+        <v>0.000747488381545123</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0247725164270442</v>
+        <v>0.0192861035473089</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0196400882473723</v>
+        <v>0.0192524366233324</v>
       </c>
       <c r="H2" t="n">
-        <v>-16779.5017064521</v>
+        <v>-20830.9408935807</v>
       </c>
       <c r="I2" t="n">
-        <v>-20521.2259010673</v>
+        <v>-21048.5697816639</v>
       </c>
     </row>
     <row r="3">
@@ -2705,16 +2643,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000814676440499745</v>
+        <v>0.0000799538304219252</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0000528715016861755</v>
+        <v>0.0000515884566718829</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00641265419972203</v>
+        <v>0.00636123562040069</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00530100746212438</v>
+        <v>0.00528514432041726</v>
       </c>
       <c r="H4" t="n">
         <v>-30840.5321645848</v>

--- a/results/consolidated/NF_vs_Standard_GARCH_Comparison.xlsx
+++ b/results/consolidated/NF_vs_Standard_GARCH_Comparison.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Overall mean MSE - NF-GARCH</t>
   </si>
   <si>
-    <t xml:space="preserve">0.000433198859237968</t>
+    <t xml:space="preserve">2.07934565878762e-06</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean AIC - Standard</t>
@@ -54,19 +54,19 @@
     <t xml:space="preserve">Overall mean AIC - NF-GARCH</t>
   </si>
   <si>
-    <t xml:space="preserve">-25835.7365290827</t>
+    <t xml:space="preserve">-16711.9848712444</t>
   </si>
   <si>
     <t xml:space="preserve">NF-GARCH wins (lower MSE)</t>
   </si>
   <si>
-    <t xml:space="preserve">6</t>
+    <t xml:space="preserve">18</t>
   </si>
   <si>
     <t xml:space="preserve">Standard GARCH wins (lower MSE)</t>
   </si>
   <si>
-    <t xml:space="preserve">12</t>
+    <t xml:space="preserve">0</t>
   </si>
   <si>
     <t xml:space="preserve">Overall winner</t>
@@ -716,43 +716,43 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>-25490.1424379366</v>
+        <v>-16492.244919545</v>
       </c>
       <c r="D2" t="n">
         <v>-25490.1424379366</v>
       </c>
       <c r="E2" t="n">
-        <v>-25451.6514751415</v>
+        <v>-16456.3401877928</v>
       </c>
       <c r="F2" t="n">
         <v>-25451.6514751415</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000353285522699968</v>
+        <v>0.00000197940386503154</v>
       </c>
       <c r="H2" t="n">
         <v>0.000559673107021087</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0112661449369954</v>
+        <v>0.000354547612450224</v>
       </c>
       <c r="J2" t="n">
         <v>0.0137454998374633</v>
       </c>
       <c r="K2" t="n">
-        <v>12751.0712189683</v>
+        <v>8252.12245977249</v>
       </c>
       <c r="L2" t="n">
         <v>12751.0712189683</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.00000000000363797880709171</v>
+        <v>-8997.8975183916</v>
       </c>
       <c r="N2" t="n">
-        <v>36.876451938103</v>
+        <v>99.6463285728401</v>
       </c>
       <c r="O2" t="n">
-        <v>18.037575423125</v>
+        <v>97.4206277207621</v>
       </c>
     </row>
     <row r="3">
@@ -794,43 +794,43 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>-27474.0650181722</v>
+        <v>-17837.3040694494</v>
       </c>
       <c r="D4" t="n">
         <v>-27474.0650181722</v>
       </c>
       <c r="E4" t="n">
-        <v>-27435.5740553771</v>
+        <v>-17801.3993376972</v>
       </c>
       <c r="F4" t="n">
         <v>-27435.5740553771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00041244704938497</v>
+        <v>0.0000019529530901871</v>
       </c>
       <c r="H4" t="n">
         <v>0.000597494046328344</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0128394160282186</v>
+        <v>0.00034042887535204</v>
       </c>
       <c r="J4" t="n">
         <v>0.0145061145911386</v>
       </c>
       <c r="K4" t="n">
-        <v>13743.0325090861</v>
+        <v>8924.6520347247</v>
       </c>
       <c r="L4" t="n">
         <v>13743.0325090861</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.00000000000727595761418343</v>
+        <v>-9636.76094872279</v>
       </c>
       <c r="N4" t="n">
-        <v>30.9705172931019</v>
+        <v>99.6731426694227</v>
       </c>
       <c r="O4" t="n">
-        <v>11.4896277183561</v>
+        <v>97.6532042869701</v>
       </c>
     </row>
     <row r="5">
@@ -841,23 +841,23 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>-25189.3693301111</v>
+        <v>-16259.1952479916</v>
       </c>
       <c r="D5"/>
       <c r="E5" t="n">
-        <v>-25160.5011080147</v>
+        <v>-16232.2666991774</v>
       </c>
       <c r="F5"/>
       <c r="G5" t="n">
-        <v>0.000483531432433468</v>
+        <v>0.00000219251283996592</v>
       </c>
       <c r="H5"/>
       <c r="I5" t="n">
-        <v>0.0135945586851025</v>
+        <v>0.000365227734608415</v>
       </c>
       <c r="J5"/>
       <c r="K5" t="n">
-        <v>12599.1846650555</v>
+        <v>8134.0976239958</v>
       </c>
       <c r="L5"/>
       <c r="M5"/>
@@ -931,13 +931,13 @@
         <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>-25835.7365290827</v>
+        <v>-16711.9848712444</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000433198859237968</v>
+        <v>0.00000207934565878762</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0128236695838548</v>
+        <v>0.000356357989254773</v>
       </c>
     </row>
     <row r="3">
@@ -990,10 +990,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -1004,10 +1004,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -1018,10 +1018,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1686,19 +1686,19 @@
         <v>60</v>
       </c>
       <c r="D21" t="n">
-        <v>-30865.1151412699</v>
+        <v>-19372.7663740109</v>
       </c>
       <c r="E21" t="n">
-        <v>-30839.4544994065</v>
+        <v>-19348.829886176</v>
       </c>
       <c r="F21" t="n">
-        <v>15436.5575706349</v>
+        <v>9690.38318700543</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0000429924605098405</v>
+        <v>0.00000000273043100974504</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00490017529074978</v>
+        <v>0.0000217422868399001</v>
       </c>
       <c r="I21" t="s">
         <v>42</v>
@@ -1718,19 +1718,19 @@
         <v>62</v>
       </c>
       <c r="D22" t="n">
-        <v>-31065.310641081</v>
+        <v>-20093.9832449172</v>
       </c>
       <c r="E22" t="n">
-        <v>-31039.6499992176</v>
+        <v>-20070.0467570823</v>
       </c>
       <c r="F22" t="n">
-        <v>15536.6553205405</v>
+        <v>10050.9916224586</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0000520595129536844</v>
+        <v>0.00000000659878676109074</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00528619064757042</v>
+        <v>0.0000339667878183346</v>
       </c>
       <c r="I22" t="s">
         <v>42</v>
@@ -1750,19 +1750,19 @@
         <v>63</v>
       </c>
       <c r="D23" t="n">
-        <v>-25662.9237836476</v>
+        <v>-16711.3634303374</v>
       </c>
       <c r="E23" t="n">
-        <v>-25637.2631417842</v>
+        <v>-16687.4269425026</v>
       </c>
       <c r="F23" t="n">
-        <v>12835.4618918238</v>
+        <v>8359.6817151687</v>
       </c>
       <c r="G23" t="n">
-        <v>0.000153700150191844</v>
+        <v>0.0000000543054865390725</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00936764893306355</v>
+        <v>0.000101048919084511</v>
       </c>
       <c r="I23" t="s">
         <v>42</v>
@@ -1782,19 +1782,19 @@
         <v>56</v>
       </c>
       <c r="D24" t="n">
-        <v>-16292.5961162957</v>
+        <v>-10849.6298936207</v>
       </c>
       <c r="E24" t="n">
-        <v>-16266.9354744323</v>
+        <v>-10825.6934057859</v>
       </c>
       <c r="F24" t="n">
-        <v>8150.29805814787</v>
+        <v>5428.81494681033</v>
       </c>
       <c r="G24" t="n">
-        <v>0.00142634329904931</v>
+        <v>0.0000100063284535015</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0272432424628154</v>
+        <v>0.00114886134291504</v>
       </c>
       <c r="I24" t="s">
         <v>42</v>
@@ -1814,19 +1814,19 @@
         <v>58</v>
       </c>
       <c r="D25" t="n">
-        <v>-21806.61635107</v>
+        <v>-13915.8189354138</v>
       </c>
       <c r="E25" t="n">
-        <v>-21780.9557092066</v>
+        <v>-13891.882447579</v>
       </c>
       <c r="F25" t="n">
-        <v>10907.308175535</v>
+        <v>6961.90946770692</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000409421267002899</v>
+        <v>0.00000120916215071281</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0144130890260051</v>
+        <v>0.000352414577502558</v>
       </c>
       <c r="I25" t="s">
         <v>42</v>
@@ -1846,19 +1846,19 @@
         <v>59</v>
       </c>
       <c r="D26" t="n">
-        <v>-17563.0888840556</v>
+        <v>-11081.523323752</v>
       </c>
       <c r="E26" t="n">
-        <v>-17537.4282421922</v>
+        <v>-11057.5868359172</v>
       </c>
       <c r="F26" t="n">
-        <v>8785.54444202782</v>
+        <v>5544.76166187601</v>
       </c>
       <c r="G26" t="n">
-        <v>0.000871937248769845</v>
+        <v>0.00000188335462307762</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0212944310569644</v>
+        <v>0.000533547851583591</v>
       </c>
       <c r="I26" t="s">
         <v>42</v>
@@ -1878,19 +1878,19 @@
         <v>60</v>
       </c>
       <c r="D27" t="n">
-        <v>-33362.8305909618</v>
+        <v>-21086.222814587</v>
       </c>
       <c r="E27" t="n">
-        <v>-33330.7547886325</v>
+        <v>-21056.3022047935</v>
       </c>
       <c r="F27" t="n">
-        <v>16686.4152954809</v>
+        <v>10548.1114072935</v>
       </c>
       <c r="G27" t="n">
-        <v>0.000042881880258254</v>
+        <v>0.00000000273041748166327</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00488461971956549</v>
+        <v>0.0000217415724608806</v>
       </c>
       <c r="I27" t="s">
         <v>42</v>
@@ -1910,19 +1910,19 @@
         <v>62</v>
       </c>
       <c r="D28" t="n">
-        <v>-33107.3400236491</v>
+        <v>-21446.4359075332</v>
       </c>
       <c r="E28" t="n">
-        <v>-33075.2642213199</v>
+        <v>-21416.5152977397</v>
       </c>
       <c r="F28" t="n">
-        <v>16558.6700118246</v>
+        <v>10728.2179537666</v>
       </c>
       <c r="G28" t="n">
-        <v>0.000052058658312496</v>
+        <v>0.00000000659878584811166</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0052840979932641</v>
+        <v>0.0000339666827343086</v>
       </c>
       <c r="I28" t="s">
         <v>42</v>
@@ -1942,19 +1942,19 @@
         <v>63</v>
       </c>
       <c r="D29" t="n">
-        <v>-27582.4054634246</v>
+        <v>-17841.2674418593</v>
       </c>
       <c r="E29" t="n">
-        <v>-27550.3296610953</v>
+        <v>-17811.3468320658</v>
       </c>
       <c r="F29" t="n">
-        <v>13796.2027317123</v>
+        <v>8925.63372092964</v>
       </c>
       <c r="G29" t="n">
-        <v>0.000153260125523895</v>
+        <v>0.0000000543050794749149</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00932006142463944</v>
+        <v>0.000101047988330443</v>
       </c>
       <c r="I29" t="s">
         <v>42</v>
@@ -1974,19 +1974,19 @@
         <v>56</v>
       </c>
       <c r="D30" t="n">
-        <v>-18896.2142759014</v>
+        <v>-12618.2868051962</v>
       </c>
       <c r="E30" t="n">
-        <v>-18864.1384735722</v>
+        <v>-12588.3661954027</v>
       </c>
       <c r="F30" t="n">
-        <v>9453.10713795071</v>
+        <v>6314.14340259809</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00139596012545205</v>
+        <v>0.00000999167627594231</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0269213319681704</v>
+        <v>0.00114854170741762</v>
       </c>
       <c r="I30" t="s">
         <v>42</v>
@@ -2006,19 +2006,19 @@
         <v>58</v>
       </c>
       <c r="D31" t="n">
-        <v>-24492.0770277156</v>
+        <v>-16187.7828771156</v>
       </c>
       <c r="E31" t="n">
-        <v>-24460.0012253864</v>
+        <v>-16157.8622673221</v>
       </c>
       <c r="F31" t="n">
-        <v>12251.0385138578</v>
+        <v>8098.89143855781</v>
       </c>
       <c r="G31" t="n">
-        <v>0.000408453415032372</v>
+        <v>0.00000120903592295575</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0143806332568695</v>
+        <v>0.000352339054425865</v>
       </c>
       <c r="I31" t="s">
         <v>42</v>
@@ -2038,19 +2038,19 @@
         <v>59</v>
       </c>
       <c r="D32" t="n">
-        <v>-21575.9136622605</v>
+        <v>-13905.261927556</v>
       </c>
       <c r="E32" t="n">
-        <v>-21543.8378599312</v>
+        <v>-13875.3413177625</v>
       </c>
       <c r="F32" t="n">
-        <v>10792.9568311302</v>
+        <v>6957.63096377799</v>
       </c>
       <c r="G32" t="n">
-        <v>0.000793309046145127</v>
+        <v>0.00000188332766628651</v>
       </c>
       <c r="H32" t="n">
-        <v>0.019839182441553</v>
+        <v>0.000533514044187929</v>
       </c>
       <c r="I32" t="s">
         <v>42</v>
@@ -2070,19 +2070,19 @@
         <v>60</v>
       </c>
       <c r="D33" t="n">
-        <v>-34582.5142602016</v>
+        <v>-21907.7870476517</v>
       </c>
       <c r="E33" t="n">
-        <v>-34544.0232974065</v>
+        <v>-21871.8823158995</v>
       </c>
       <c r="F33" t="n">
-        <v>17297.2571301008</v>
+        <v>10959.8935238259</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0000389270752310303</v>
+        <v>0.00000000264905855532464</v>
       </c>
       <c r="H33" t="n">
-        <v>0.004634694296471</v>
+        <v>0.0000199526902019476</v>
       </c>
       <c r="I33" t="s">
         <v>42</v>
@@ -2102,19 +2102,19 @@
         <v>62</v>
       </c>
       <c r="D34" t="n">
-        <v>-34124.7483549712</v>
+        <v>-22126.0079652002</v>
       </c>
       <c r="E34" t="n">
-        <v>-34086.2573921761</v>
+        <v>-22090.103233448</v>
       </c>
       <c r="F34" t="n">
-        <v>17068.3741774856</v>
+        <v>11069.0039826001</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0000511182550312698</v>
+        <v>0.00000000631580908854966</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0053035667901323</v>
+        <v>0.0000311074353849485</v>
       </c>
       <c r="I34" t="s">
         <v>42</v>
@@ -2134,19 +2134,19 @@
         <v>63</v>
       </c>
       <c r="D35" t="n">
-        <v>-28687.4162221169</v>
+        <v>-18500.777830922</v>
       </c>
       <c r="E35" t="n">
-        <v>-28648.9252593218</v>
+        <v>-18464.8730991698</v>
       </c>
       <c r="F35" t="n">
-        <v>14349.7081110585</v>
+        <v>9256.38891546099</v>
       </c>
       <c r="G35" t="n">
-        <v>0.000179474887527678</v>
+        <v>0.0000000333883423762622</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0104374757850525</v>
+        <v>0.0000903674333894644</v>
       </c>
       <c r="I35" t="s">
         <v>42</v>
@@ -2166,19 +2166,19 @@
         <v>56</v>
       </c>
       <c r="D36" t="n">
-        <v>-19808.0176404271</v>
+        <v>-13273.652880235</v>
       </c>
       <c r="E36" t="n">
-        <v>-19769.526677632</v>
+        <v>-13237.7481484828</v>
       </c>
       <c r="F36" t="n">
-        <v>9910.00882021353</v>
+        <v>6642.82644011749</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00113138411916276</v>
+        <v>0.00000878994316463406</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0242058272469228</v>
+        <v>0.001097890616231</v>
       </c>
       <c r="I36" t="s">
         <v>42</v>
@@ -2198,19 +2198,19 @@
         <v>58</v>
       </c>
       <c r="D37" t="n">
-        <v>-25241.6100567978</v>
+        <v>-16722.1397768847</v>
       </c>
       <c r="E37" t="n">
-        <v>-25203.1190940027</v>
+        <v>-16686.2350451324</v>
       </c>
       <c r="F37" t="n">
-        <v>12626.8050283989</v>
+        <v>8367.06988844233</v>
       </c>
       <c r="G37" t="n">
-        <v>0.000372110242411962</v>
+        <v>0.00000120517161392212</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0137892412456215</v>
+        <v>0.00033832332513122</v>
       </c>
       <c r="I37" t="s">
         <v>42</v>
@@ -2230,19 +2230,19 @@
         <v>59</v>
       </c>
       <c r="D38" t="n">
-        <v>-22400.0835745185</v>
+        <v>-14493.4589158028</v>
       </c>
       <c r="E38" t="n">
-        <v>-22361.5926117234</v>
+        <v>-14457.5541840505</v>
       </c>
       <c r="F38" t="n">
-        <v>11206.0417872593</v>
+        <v>7252.72945790138</v>
       </c>
       <c r="G38" t="n">
-        <v>0.000701667716945119</v>
+        <v>0.0000016802505525463</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0186656908051118</v>
+        <v>0.00046493175177366</v>
       </c>
       <c r="I38" t="s">
         <v>42</v>
@@ -2262,19 +2262,19 @@
         <v>60</v>
       </c>
       <c r="D39" t="n">
-        <v>-32326.2491294199</v>
+        <v>-20390.7246340714</v>
       </c>
       <c r="E39" t="n">
-        <v>-32287.7581666248</v>
+        <v>-20354.8199023192</v>
       </c>
       <c r="F39" t="n">
-        <v>16169.12456471</v>
+        <v>10201.3623170357</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0000344213950678341</v>
+        <v>0.00000000287231289027716</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00423485074942777</v>
+        <v>0.0000220725090305658</v>
       </c>
       <c r="I39" t="s">
         <v>42</v>
@@ -2294,19 +2294,19 @@
         <v>62</v>
       </c>
       <c r="D40" t="n">
-        <v>-31954.3769009613</v>
+        <v>-20663.0629217926</v>
       </c>
       <c r="E40" t="n">
-        <v>-31915.8859381662</v>
+        <v>-20627.1581900404</v>
       </c>
       <c r="F40" t="n">
-        <v>15983.1884504807</v>
+        <v>10337.5314608963</v>
       </c>
       <c r="G40" t="n">
-        <v>0.000040961652767101</v>
+        <v>0.00000000684221974618736</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00452963118836436</v>
+        <v>0.0000342989225345756</v>
       </c>
       <c r="I40" t="s">
         <v>42</v>
@@ -2326,19 +2326,19 @@
         <v>63</v>
       </c>
       <c r="D41" t="n">
-        <v>-26765.1554633125</v>
+        <v>-17296.0175829807</v>
       </c>
       <c r="E41" t="n">
-        <v>-26726.6645005174</v>
+        <v>-17260.1128512285</v>
       </c>
       <c r="F41" t="n">
-        <v>13388.5777316562</v>
+        <v>8654.00879149036</v>
       </c>
       <c r="G41" t="n">
-        <v>0.000117589911688175</v>
+        <v>0.000000041989390640004</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00815181462650758</v>
+        <v>0.0000979222749789158</v>
       </c>
       <c r="I41" t="s">
         <v>42</v>
@@ -2358,19 +2358,19 @@
         <v>56</v>
       </c>
       <c r="D42" t="n">
-        <v>-17940.7188127727</v>
+        <v>-11957.8877932379</v>
       </c>
       <c r="E42" t="n">
-        <v>-17902.2278499776</v>
+        <v>-11921.9830614857</v>
       </c>
       <c r="F42" t="n">
-        <v>8976.35940638635</v>
+        <v>5984.94389661896</v>
       </c>
       <c r="G42" t="n">
-        <v>0.00101199956331745</v>
+        <v>0.00000884643765804399</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0221733143992038</v>
+        <v>0.00111799097086115</v>
       </c>
       <c r="I42" t="s">
         <v>42</v>
@@ -2390,19 +2390,19 @@
         <v>58</v>
       </c>
       <c r="D43" t="n">
-        <v>-23433.1284200857</v>
+        <v>-15439.990288026</v>
       </c>
       <c r="E43" t="n">
-        <v>-23394.6374572906</v>
+        <v>-15404.0855562738</v>
       </c>
       <c r="F43" t="n">
-        <v>11722.5642100428</v>
+        <v>7725.99514401299</v>
       </c>
       <c r="G43" t="n">
-        <v>0.00031699205138684</v>
+        <v>0.00000123092826164175</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0121101815907052</v>
+        <v>0.000357952396258783</v>
       </c>
       <c r="I43" t="s">
         <v>42</v>
@@ -2422,19 +2422,19 @@
         <v>59</v>
       </c>
       <c r="D44" t="n">
-        <v>-20521.2259010673</v>
+        <v>-13205.7862971612</v>
       </c>
       <c r="E44" t="n">
-        <v>-20482.7349382722</v>
+        <v>-13169.881565409</v>
       </c>
       <c r="F44" t="n">
-        <v>10266.6129505337</v>
+        <v>6608.89314858061</v>
       </c>
       <c r="G44" t="n">
-        <v>0.000597748561972406</v>
+        <v>0.00000174735334722701</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0163970770677635</v>
+        <v>0.000497048601037352</v>
       </c>
       <c r="I44" t="s">
         <v>42</v>
@@ -2482,13 +2482,13 @@
         <v>70</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.015625</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="s">
         <v>71</v>
@@ -2502,13 +2502,13 @@
         <v>70</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.015625</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
         <v>71</v>
@@ -2522,13 +2522,13 @@
         <v>70</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.015625</v>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="s">
         <v>71</v>
@@ -2585,22 +2585,22 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000786443888054012</v>
+        <v>0.00000414024747420764</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000747488381545123</v>
+        <v>0.00000181534050675676</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0192861035473089</v>
+        <v>0.000661946353277147</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0192524366233324</v>
+        <v>0.000515281322612641</v>
       </c>
       <c r="H2" t="n">
-        <v>-20830.9408935807</v>
+        <v>-13637.6016428335</v>
       </c>
       <c r="I2" t="n">
-        <v>-21048.5697816639</v>
+        <v>-13589.4574038955</v>
       </c>
     </row>
     <row r="3">
@@ -2643,22 +2643,22 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000799538304219252</v>
+        <v>0.0000000184438433676003</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0000515884566718829</v>
+        <v>0.0000000065987863046012</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00636123562040069</v>
+        <v>0.0000507696252323996</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00528514432041726</v>
+        <v>0.0000339667352763216</v>
       </c>
       <c r="H4" t="n">
-        <v>-30840.5321645848</v>
+        <v>-19786.3680996553</v>
       </c>
       <c r="I4" t="n">
-        <v>-31509.8437710212</v>
+        <v>-20242.3539394943</v>
       </c>
     </row>
     <row r="5">
@@ -2723,37 +2723,23 @@
         <v>42</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>33.3333333333333</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="n">
         <v>100</v>
       </c>
     </row>

--- a/results/consolidated/NF_vs_Standard_GARCH_Comparison.xlsx
+++ b/results/consolidated/NF_vs_Standard_GARCH_Comparison.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t xml:space="preserve">Question</t>
   </si>
@@ -36,37 +36,34 @@
     <t xml:space="preserve">Overall mean MSE - Standard</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50174528626368</t>
+    <t xml:space="preserve">2.52760105032062e+137</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean MSE - NF-GARCH</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07934565878762e-06</t>
+    <t xml:space="preserve">0.00170545178299988</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean AIC - Standard</t>
   </si>
   <si>
-    <t xml:space="preserve">-23419.1714337619</t>
+    <t xml:space="preserve">-15940.078354814</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean AIC - NF-GARCH</t>
   </si>
   <si>
-    <t xml:space="preserve">-16711.9848712444</t>
-  </si>
-  <si>
     <t xml:space="preserve">NF-GARCH wins (lower MSE)</t>
   </si>
   <si>
-    <t xml:space="preserve">18</t>
+    <t xml:space="preserve">24</t>
   </si>
   <si>
     <t xml:space="preserve">Standard GARCH wins (lower MSE)</t>
   </si>
   <si>
-    <t xml:space="preserve">0</t>
+    <t xml:space="preserve">1</t>
   </si>
   <si>
     <t xml:space="preserve">Overall winner</t>
@@ -78,6 +75,9 @@
     <t xml:space="preserve">Model</t>
   </si>
   <si>
+    <t xml:space="preserve">Distribution</t>
+  </si>
+  <si>
     <t xml:space="preserve">n_assets</t>
   </si>
   <si>
@@ -123,6 +123,9 @@
     <t xml:space="preserve">TGARCH</t>
   </si>
   <si>
+    <t xml:space="preserve">sstd</t>
+  </si>
+  <si>
     <t xml:space="preserve">eGARCH</t>
   </si>
   <si>
@@ -132,6 +135,9 @@
     <t xml:space="preserve">sGARCH</t>
   </si>
   <si>
+    <t xml:space="preserve">norm</t>
+  </si>
+  <si>
     <t xml:space="preserve">Source</t>
   </si>
   <si>
@@ -162,9 +168,6 @@
     <t xml:space="preserve">win_rate</t>
   </si>
   <si>
-    <t xml:space="preserve">Distribution</t>
-  </si>
-  <si>
     <t xml:space="preserve">Asset</t>
   </si>
   <si>
@@ -183,12 +186,15 @@
     <t xml:space="preserve">MAE</t>
   </si>
   <si>
+    <t xml:space="preserve">PredictiveLogLik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPaths</t>
+  </si>
+  <si>
     <t xml:space="preserve">Asset_Class</t>
   </si>
   <si>
-    <t xml:space="preserve">sstd</t>
-  </si>
-  <si>
     <t xml:space="preserve">NVDA</t>
   </si>
   <si>
@@ -211,9 +217,6 @@
   </si>
   <si>
     <t xml:space="preserve">USDZAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">norm</t>
   </si>
   <si>
     <t xml:space="preserve">Test_Type</t>
@@ -623,31 +626,31 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -663,48 +666,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>23</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>26</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -712,188 +718,251 @@
       <c r="A2" t="s">
         <v>33</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="n">
         <v>6</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>-16492.244919545</v>
       </c>
-      <c r="D2" t="n">
-        <v>-25490.1424379366</v>
-      </c>
       <c r="E2" t="n">
+        <v>-16492.244919545</v>
+      </c>
+      <c r="F2" t="n">
         <v>-16456.3401877928</v>
       </c>
-      <c r="F2" t="n">
-        <v>-25451.6514751415</v>
-      </c>
       <c r="G2" t="n">
-        <v>0.00000197940386503154</v>
+        <v>-16456.3401877928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000559673107021087</v>
+        <v>0.000354956494493567</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000354547612450224</v>
+        <v>59443726319534449280006002206028424662</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0137454998374633</v>
+        <v>0.0114916145174231</v>
       </c>
       <c r="K2" t="n">
+        <v>495480725121196672</v>
+      </c>
+      <c r="L2" t="n">
         <v>8252.12245977249</v>
       </c>
-      <c r="L2" t="n">
-        <v>12751.0712189683</v>
-      </c>
       <c r="M2" t="n">
-        <v>-8997.8975183916</v>
+        <v>8252.12245977249</v>
       </c>
       <c r="N2" t="n">
-        <v>99.6463285728401</v>
+        <v>-0.0000000000109139364212751</v>
       </c>
       <c r="O2" t="n">
-        <v>97.4206277207621</v>
+        <v>100</v>
+      </c>
+      <c r="P2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="C3"/>
       <c r="D3" t="n">
-        <v>31837.7685390903</v>
-      </c>
-      <c r="E3"/>
+        <v>635.787255489474</v>
+      </c>
+      <c r="E3" t="n">
+        <v>635.787255489474</v>
+      </c>
       <c r="F3" t="n">
-        <v>31876.2595018854</v>
-      </c>
-      <c r="G3"/>
+        <v>671.691987241692</v>
+      </c>
+      <c r="G3" t="n">
+        <v>671.691987241692</v>
+      </c>
       <c r="H3" t="n">
-        <v>66.5223139166787</v>
-      </c>
-      <c r="I3"/>
+        <v>0.0340401235620799</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6319002625801544635622286848826426420822064026860400222086266606486846066284682406648224486460668628846026024882080400848446860806626608662</v>
+      </c>
       <c r="J3" t="n">
-        <v>1.54717433862132</v>
-      </c>
-      <c r="K3"/>
+        <v>0.136455701792049</v>
+      </c>
+      <c r="K3" t="n">
+        <v>216996834662478079722482026088480064066884602844262466420888604862226</v>
+      </c>
       <c r="L3" t="n">
-        <v>-15912.8842695452</v>
-      </c>
-      <c r="M3"/>
-      <c r="N3"/>
-      <c r="O3"/>
+        <v>-311.893627744737</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-311.893627744737</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.000000000000227373675443232</v>
+      </c>
+      <c r="O3" t="n">
+        <v>100</v>
+      </c>
+      <c r="P3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="n">
         <v>6</v>
       </c>
-      <c r="C4" t="n">
-        <v>-17837.3040694494</v>
-      </c>
       <c r="D4" t="n">
-        <v>-27474.0650181722</v>
+        <v>-17512.3222721118</v>
       </c>
       <c r="E4" t="n">
-        <v>-17801.3993376972</v>
+        <v>-17512.3222721118</v>
       </c>
       <c r="F4" t="n">
-        <v>-27435.5740553771</v>
+        <v>-17476.4175403596</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0000019529530901871</v>
+        <v>-17476.4175403596</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000597494046328344</v>
+        <v>0.000354359301181795</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00034042887535204</v>
+        <v>0.0004457363014615</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0145061145911386</v>
+        <v>0.0114872701330868</v>
       </c>
       <c r="K4" t="n">
-        <v>8924.6520347247</v>
+        <v>0.0126079045451664</v>
       </c>
       <c r="L4" t="n">
-        <v>13743.0325090861</v>
+        <v>8762.1611360559</v>
       </c>
       <c r="M4" t="n">
-        <v>-9636.76094872279</v>
+        <v>8762.16113605591</v>
       </c>
       <c r="N4" t="n">
-        <v>99.6731426694227</v>
+        <v>-0.00000000000363797880709171</v>
       </c>
       <c r="O4" t="n">
-        <v>97.6532042869701</v>
+        <v>20.5002374677796</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8.88834784610695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" t="n">
-        <v>12</v>
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>-16259.1952479916</v>
-      </c>
-      <c r="D5"/>
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-15337.514200342</v>
+      </c>
       <c r="E5" t="n">
-        <v>-16232.2666991774</v>
-      </c>
-      <c r="F5"/>
+        <v>-15337.514200342</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-15313.5777125072</v>
+      </c>
       <c r="G5" t="n">
-        <v>0.00000219251283996592</v>
-      </c>
-      <c r="H5"/>
+        <v>-15313.5777125072</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.000369080617213171</v>
+      </c>
       <c r="I5" t="n">
-        <v>0.000365227734608415</v>
-      </c>
-      <c r="J5"/>
+        <v>3.29130484982847</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0117845885225423</v>
+      </c>
       <c r="K5" t="n">
-        <v>8134.0976239958</v>
-      </c>
-      <c r="L5"/>
-      <c r="M5"/>
-      <c r="N5"/>
-      <c r="O5"/>
+        <v>0.317372015862975</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7672.757100171</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7672.75710017099</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.00000000000909494701772928</v>
+      </c>
+      <c r="O5" t="n">
+        <v>99.9887861916762</v>
+      </c>
+      <c r="P5" t="n">
+        <v>96.2868217947639</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="n">
         <v>6</v>
       </c>
-      <c r="C6"/>
       <c r="D6" t="n">
-        <v>-26502.7968406522</v>
-      </c>
-      <c r="E6"/>
+        <v>-17180.8762956412</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-17180.8762956412</v>
+      </c>
       <c r="F6" t="n">
-        <v>-26470.7210383229</v>
-      </c>
-      <c r="G6"/>
+        <v>-17150.9556858477</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-17150.9556858477</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.000650586568502746</v>
-      </c>
-      <c r="I6"/>
+        <v>0.00035429875593098</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.5559196884804</v>
+      </c>
       <c r="J6" t="n">
-        <v>0.0153865953175631</v>
-      </c>
-      <c r="K6"/>
+        <v>0.011480154573704</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.205412486841088</v>
+      </c>
       <c r="L6" t="n">
-        <v>13256.3984203261</v>
-      </c>
-      <c r="M6"/>
-      <c r="N6"/>
-      <c r="O6"/>
+        <v>8595.43814782061</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8595.43814782061</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.00000000000363797880709171</v>
+      </c>
+      <c r="O6" t="n">
+        <v>99.9900363678888</v>
+      </c>
+      <c r="P6" t="n">
+        <v>94.4111700557983</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -908,53 +977,53 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>-16711.9848712444</v>
+        <v>-15940.078354814</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00000207934565878762</v>
+        <v>0.00170545178299988</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000356357989254773</v>
+        <v>0.0165566987309035</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>-23419.1714337619</v>
+        <v>-15940.078354814</v>
       </c>
       <c r="D3" t="n">
-        <v>3.50174528626368</v>
+        <v>252760105032061765680848840286000462602800260064088682068208860286084808404608640882402804864864222028224468086444628226428480862442486848</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0952107156367529</v>
+        <v>8679873386499122659400606262886664840246688000868226606248880602082</v>
       </c>
     </row>
   </sheetData>
@@ -970,29 +1039,35 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" t="s">
-        <v>44</v>
-      </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="E1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>33</v>
       </c>
-      <c r="B2" t="n">
-        <v>6</v>
+      <c r="B2" t="s">
+        <v>34</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1000,13 +1075,16 @@
       <c r="A3" t="s">
         <v>35</v>
       </c>
-      <c r="B3" t="n">
-        <v>6</v>
+      <c r="B3" t="s">
+        <v>34</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1014,13 +1092,50 @@
       <c r="A4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" t="n">
-        <v>6</v>
+      <c r="B4" t="s">
+        <v>34</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>83.3333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1037,130 +1152,154 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" t="s">
-        <v>47</v>
-      </c>
       <c r="C1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I1" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="J1" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="K1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D2" t="n">
-        <v>-18896.2142759014</v>
+        <v>-10849.6298936207</v>
       </c>
       <c r="E2" t="n">
-        <v>-18864.1384735722</v>
+        <v>-10825.6934057859</v>
       </c>
       <c r="F2" t="n">
-        <v>9453.10713795071</v>
+        <v>5428.81494681033</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00215198175295782</v>
+        <v>0.601409767741544</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0379765477640055</v>
-      </c>
-      <c r="I2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" t="s">
-        <v>57</v>
+        <v>0.252193599528106</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5270.53498430595</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D3" t="n">
-        <v>-17940.7188127727</v>
+        <v>-12618.2868051962</v>
       </c>
       <c r="E3" t="n">
-        <v>-17902.2278499776</v>
+        <v>-12588.3661954027</v>
       </c>
       <c r="F3" t="n">
-        <v>8976.35940638635</v>
+        <v>6314.14340259809</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00230675155226541</v>
+        <v>20.3333406429236</v>
       </c>
       <c r="H3" t="n">
-        <v>0.038889301382911</v>
-      </c>
-      <c r="I3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" t="s">
-        <v>57</v>
+        <v>0.620988161819819</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5038.99852606956</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D4" t="n">
-        <v>-19808.0176404271</v>
+        <v>-11957.8877932379</v>
       </c>
       <c r="E4" t="n">
-        <v>-19769.526677632</v>
+        <v>-11921.9830614857</v>
       </c>
       <c r="F4" t="n">
-        <v>9910.00882021353</v>
+        <v>5984.94389661896</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00211018578744319</v>
+        <v>33659430548004201794266822262</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0373301138957993</v>
-      </c>
-      <c r="I4" t="s">
-        <v>43</v>
-      </c>
-      <c r="J4" t="s">
-        <v>57</v>
+        <v>20990175346511.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>179.702416351401</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -1168,255 +1307,303 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
         <v>58</v>
       </c>
       <c r="D5" t="n">
-        <v>-24492.0770277156</v>
+        <v>-13272.5886735945</v>
       </c>
       <c r="E5" t="n">
-        <v>-24460.0012253864</v>
+        <v>-13236.6839418423</v>
       </c>
       <c r="F5" t="n">
-        <v>12251.0385138578</v>
+        <v>6642.29433679725</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000214052529008687</v>
+        <v>0.00111720183913927</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0123577724835287</v>
-      </c>
-      <c r="I5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" t="s">
-        <v>57</v>
+        <v>0.0243034240346594</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3115.10876424277</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>-23433.1284200857</v>
+        <v>-13915.8189354138</v>
       </c>
       <c r="E6" t="n">
-        <v>-23394.6374572906</v>
+        <v>-13891.882447579</v>
       </c>
       <c r="F6" t="n">
-        <v>11722.5642100428</v>
+        <v>6961.90946770692</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000190643641792287</v>
+        <v>8.13263734830384</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0116709555045471</v>
-      </c>
-      <c r="I6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" t="s">
-        <v>57</v>
+        <v>0.470386080763109</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6035.84043645253</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D7" t="n">
-        <v>-25241.6100567978</v>
+        <v>-16187.7828771156</v>
       </c>
       <c r="E7" t="n">
-        <v>-25203.1190940027</v>
+        <v>-16157.8622673221</v>
       </c>
       <c r="F7" t="n">
-        <v>12626.8050283989</v>
+        <v>8098.89143855781</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000202318443787235</v>
+        <v>0.0269172399176276</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0121563983859576</v>
-      </c>
-      <c r="I7" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" t="s">
-        <v>57</v>
+        <v>0.0561841775044956</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5947.46170065369</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-15439.990288026</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-15404.0855562738</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7725.99514401299</v>
+      </c>
+      <c r="G8" t="n">
+        <v>356662357876333763744642020668642422202</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2972835482014035968</v>
+      </c>
+      <c r="I8" t="n">
+        <v>265.831597174635</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" t="s">
         <v>59</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-21575.9136622605</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-21543.8378599312</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10792.9568311302</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.00136378671267644</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.024167600004826</v>
-      </c>
-      <c r="I8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-16714.5673553433</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-16678.6626235911</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8363.28367767167</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.000357626028317543</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0133198188840382</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4094.40631066088</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" t="s">
         <v>59</v>
-      </c>
-      <c r="D9" t="n">
-        <v>31837.7685390903</v>
-      </c>
-      <c r="E9" t="n">
-        <v>31876.2595018854</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-15912.8842695452</v>
-      </c>
-      <c r="G9" t="n">
-        <v>66.5223139166787</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.54717433862132</v>
-      </c>
-      <c r="I9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-11081.523323752</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-11057.5868359172</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5544.76166187601</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.51076521992263</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.411565100315132</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5538.70650814066</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K10" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" t="s">
         <v>59</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-20521.2259010673</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-20482.7349382722</v>
-      </c>
-      <c r="F10" t="n">
-        <v>10266.6129505337</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.000763752779893336</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0189807701467755</v>
-      </c>
-      <c r="I10" t="s">
-        <v>43</v>
-      </c>
-      <c r="J10" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-13905.261927556</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-13875.3413177625</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6957.63096377799</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.366918678159065</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.163903114402675</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5678.53245618295</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L11" t="s">
         <v>59</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-22400.0835745185</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-22361.5926117234</v>
-      </c>
-      <c r="F11" t="n">
-        <v>11206.0417872593</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.00113419412035401</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0223531069541706</v>
-      </c>
-      <c r="I11" t="s">
-        <v>43</v>
-      </c>
-      <c r="J11" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>-33362.8305909618</v>
+        <v>635.787255489474</v>
       </c>
       <c r="E12" t="n">
-        <v>-33330.7547886325</v>
+        <v>671.691987241692</v>
       </c>
       <c r="F12" t="n">
-        <v>16686.4152954809</v>
+        <v>-311.893627744737</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0000422722623772161</v>
+        <v>6319002625801544635622286848826426420822064026860400222086266606486846066284682406648224486460668628846026024882080400848446860806626608662</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00542817692859459</v>
-      </c>
-      <c r="I12" t="s">
-        <v>43</v>
-      </c>
-      <c r="J12" t="s">
-        <v>61</v>
+        <v>216996834662478079722482026088480064066884602844262466420888604862226</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7510.19102579582</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K12" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -1424,159 +1611,189 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>-32326.2491294199</v>
+        <v>-13205.7862971612</v>
       </c>
       <c r="E13" t="n">
-        <v>-32287.7581666248</v>
+        <v>-13169.881565409</v>
       </c>
       <c r="F13" t="n">
-        <v>16169.12456471</v>
+        <v>6608.89314858061</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000024858777069834</v>
+        <v>1195319065165623506266802266</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00406191649185466</v>
-      </c>
-      <c r="I13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J13" t="s">
-        <v>61</v>
+        <v>9484050436284.61</v>
+      </c>
+      <c r="I13" t="n">
+        <v>100.531728338937</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K13" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D14" t="n">
-        <v>-34582.5142602016</v>
+        <v>-14011.7133296657</v>
       </c>
       <c r="E14" t="n">
-        <v>-34544.0232974065</v>
+        <v>-13975.8085979135</v>
       </c>
       <c r="F14" t="n">
-        <v>17297.2571301008</v>
+        <v>7011.85666483284</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0000267578797105093</v>
+        <v>0.000544228252986239</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0042450695744421</v>
-      </c>
-      <c r="I14" t="s">
-        <v>43</v>
-      </c>
-      <c r="J14" t="s">
-        <v>61</v>
+        <v>0.0168477859626725</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4100.46093900027</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K14" t="s">
+        <v>45</v>
+      </c>
+      <c r="L14" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
         <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>-33107.3400236491</v>
+        <v>-19372.7663740109</v>
       </c>
       <c r="E15" t="n">
-        <v>-33075.2642213199</v>
+        <v>-19348.829886176</v>
       </c>
       <c r="F15" t="n">
-        <v>16558.6700118246</v>
+        <v>9690.38318700543</v>
       </c>
       <c r="G15" t="n">
-        <v>0.000033297307957778</v>
+        <v>7.39654709151959</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00451548259175802</v>
-      </c>
-      <c r="I15" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" t="s">
-        <v>61</v>
+        <v>0.593515941331431</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7795.02636457378</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K15" t="s">
+        <v>45</v>
+      </c>
+      <c r="L15" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
         <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>-31954.3769009613</v>
+        <v>-21086.222814587</v>
       </c>
       <c r="E16" t="n">
-        <v>-31915.8859381662</v>
+        <v>-21056.3022047935</v>
       </c>
       <c r="F16" t="n">
-        <v>15983.1884504807</v>
+        <v>10548.1114072935</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0000184975556513942</v>
+        <v>0.182363083709309</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00328387418685859</v>
-      </c>
-      <c r="I16" t="s">
-        <v>43</v>
-      </c>
-      <c r="J16" t="s">
-        <v>61</v>
+        <v>0.156067440893827</v>
+      </c>
+      <c r="I16" t="n">
+        <v>7829.68128972402</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K16" t="s">
+        <v>45</v>
+      </c>
+      <c r="L16" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
         <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>-34124.7483549712</v>
+        <v>-20390.7246340714</v>
       </c>
       <c r="E17" t="n">
-        <v>-34086.2573921761</v>
+        <v>-20354.8199023192</v>
       </c>
       <c r="F17" t="n">
-        <v>17068.3741774856</v>
+        <v>10201.3623170357</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0000229257923821103</v>
+        <v>5020070539752685951688286862</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00367871535712302</v>
-      </c>
-      <c r="I17" t="s">
-        <v>43</v>
-      </c>
-      <c r="J17" t="s">
-        <v>61</v>
+        <v>13010544887916.1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2040.23721636389</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K17" t="s">
+        <v>45</v>
+      </c>
+      <c r="L17" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="18">
@@ -1584,127 +1801,151 @@
         <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-21219.4284734558</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-21183.5237417036</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10615.7142367279</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.000287481693506639</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.00618474393245327</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6539.2203797</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K18" t="s">
+        <v>45</v>
+      </c>
+      <c r="L18" t="s">
         <v>63</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-27582.4054634246</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-27550.3296610953</v>
-      </c>
-      <c r="F18" t="n">
-        <v>13796.2027317123</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.0000981288460385293</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.00787399213266571</v>
-      </c>
-      <c r="I18" t="s">
-        <v>43</v>
-      </c>
-      <c r="J18" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-20093.9832449172</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-20070.0467570823</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10050.9916224586</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0434668026779057</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0615510932204801</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7536.74279232573</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K19" t="s">
+        <v>45</v>
+      </c>
+      <c r="L19" t="s">
         <v>63</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-26765.1554633125</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-26726.6645005174</v>
-      </c>
-      <c r="F19" t="n">
-        <v>13388.5777316562</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.0000535343354542533</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.00558618131183317</v>
-      </c>
-      <c r="I19" t="s">
-        <v>43</v>
-      </c>
-      <c r="J19" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-21446.4359075332</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-21416.5152977397</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10728.2179537666</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0816884917040117</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0581959240540824</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7639.43295754841</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K20" t="s">
+        <v>45</v>
+      </c>
+      <c r="L20" t="s">
         <v>63</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-28687.4162221169</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-28648.9252593218</v>
-      </c>
-      <c r="F20" t="n">
-        <v>14349.7081110585</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.0000885822542930029</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.00727328337933892</v>
-      </c>
-      <c r="I20" t="s">
-        <v>43</v>
-      </c>
-      <c r="J20" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
         <v>64</v>
       </c>
-      <c r="C21" t="s">
-        <v>60</v>
-      </c>
       <c r="D21" t="n">
-        <v>-19372.7663740109</v>
+        <v>-20663.0629217926</v>
       </c>
       <c r="E21" t="n">
-        <v>-19348.829886176</v>
+        <v>-20627.1581900404</v>
       </c>
       <c r="F21" t="n">
-        <v>9690.38318700543</v>
+        <v>10337.5314608963</v>
       </c>
       <c r="G21" t="n">
-        <v>0.00000000273043100974504</v>
+        <v>997999452034110633222806668</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0000217422868399001</v>
-      </c>
-      <c r="I21" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" t="s">
-        <v>61</v>
+        <v>5323836690529.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1669.3534648896</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K21" t="s">
+        <v>45</v>
+      </c>
+      <c r="L21" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="22">
@@ -1712,42 +1953,48 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
         <v>64</v>
       </c>
-      <c r="C22" t="s">
-        <v>62</v>
-      </c>
       <c r="D22" t="n">
-        <v>-20093.9832449172</v>
+        <v>-21922.1562477529</v>
       </c>
       <c r="E22" t="n">
-        <v>-20070.0467570823</v>
+        <v>-21886.2515160007</v>
       </c>
       <c r="F22" t="n">
-        <v>10050.9916224586</v>
+        <v>10967.0781238764</v>
       </c>
       <c r="G22" t="n">
-        <v>0.00000000659878676109074</v>
+        <v>0.0000344080730827349</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0000339667878183346</v>
-      </c>
-      <c r="I22" t="s">
-        <v>42</v>
-      </c>
-      <c r="J22" t="s">
-        <v>61</v>
+        <v>0.00432211437089372</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5911.81214850415</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K22" t="s">
+        <v>45</v>
+      </c>
+      <c r="L22" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D23" t="n">
         <v>-16711.3634303374</v>
@@ -1759,80 +2006,98 @@
         <v>8359.6817151687</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0000000543054865390725</v>
+        <v>0.0630028688052877</v>
       </c>
       <c r="H23" t="n">
-        <v>0.000101048919084511</v>
-      </c>
-      <c r="I23" t="s">
-        <v>42</v>
-      </c>
-      <c r="J23" t="s">
-        <v>61</v>
+        <v>0.115020280019591</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6675.6358360275</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K23" t="s">
+        <v>45</v>
+      </c>
+      <c r="L23" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D24" t="n">
-        <v>-10849.6298936207</v>
+        <v>-17841.2674418593</v>
       </c>
       <c r="E24" t="n">
-        <v>-10825.6934057859</v>
+        <v>-17811.3468320658</v>
       </c>
       <c r="F24" t="n">
-        <v>5428.81494681033</v>
+        <v>8925.63372092964</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0000100063284535015</v>
+        <v>0.344289994468813</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00114886134291504</v>
-      </c>
-      <c r="I24" t="s">
-        <v>42</v>
-      </c>
-      <c r="J24" t="s">
-        <v>57</v>
+        <v>0.177136102371628</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6640.61148047267</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K24" t="s">
+        <v>45</v>
+      </c>
+      <c r="L24" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D25" t="n">
-        <v>-13915.8189354138</v>
+        <v>-17296.0175829807</v>
       </c>
       <c r="E25" t="n">
-        <v>-13891.882447579</v>
+        <v>-17260.1128512285</v>
       </c>
       <c r="F25" t="n">
-        <v>6961.90946770692</v>
+        <v>8654.00879149036</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00000120916215071281</v>
+        <v>106016510668686311296088</v>
       </c>
       <c r="H25" t="n">
-        <v>0.000352414577502558</v>
-      </c>
-      <c r="I25" t="s">
-        <v>42</v>
-      </c>
-      <c r="J25" t="s">
-        <v>57</v>
+        <v>60105782868.1831</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1564.83509158342</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K25" t="s">
+        <v>45</v>
+      </c>
+      <c r="L25" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="26">
@@ -1840,607 +2105,987 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D26" t="n">
-        <v>-11081.523323752</v>
+        <v>-17933.4795528587</v>
       </c>
       <c r="E26" t="n">
-        <v>-11057.5868359172</v>
+        <v>-17897.5748211065</v>
       </c>
       <c r="F26" t="n">
-        <v>5544.76166187601</v>
+        <v>8972.73977642934</v>
       </c>
       <c r="G26" t="n">
-        <v>0.00000188335462307762</v>
+        <v>0.000333471921736581</v>
       </c>
       <c r="H26" t="n">
-        <v>0.000533547851583591</v>
-      </c>
-      <c r="I26" t="s">
-        <v>42</v>
-      </c>
-      <c r="J26" t="s">
-        <v>57</v>
+        <v>0.010669540086281</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5310.20657263366</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K26" t="s">
+        <v>45</v>
+      </c>
+      <c r="L26" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D27" t="n">
-        <v>-21086.222814587</v>
+        <v>-19372.7663740109</v>
       </c>
       <c r="E27" t="n">
-        <v>-21056.3022047935</v>
+        <v>-19348.829886176</v>
       </c>
       <c r="F27" t="n">
-        <v>10548.1114072935</v>
+        <v>9690.38318700543</v>
       </c>
       <c r="G27" t="n">
-        <v>0.00000000273041748166327</v>
+        <v>0.0000221142231310187</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0000217415724608806</v>
-      </c>
-      <c r="I27" t="s">
-        <v>42</v>
-      </c>
-      <c r="J27" t="s">
-        <v>61</v>
+        <v>0.00350130435394098</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6150.84566075275</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L27" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>-21446.4359075332</v>
+        <v>-20093.9832449172</v>
       </c>
       <c r="E28" t="n">
-        <v>-21416.5152977397</v>
+        <v>-20070.0467570823</v>
       </c>
       <c r="F28" t="n">
-        <v>10728.2179537666</v>
+        <v>10050.9916224586</v>
       </c>
       <c r="G28" t="n">
-        <v>0.00000000659878584811166</v>
+        <v>0.0000342891762629105</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0000339666827343086</v>
-      </c>
-      <c r="I28" t="s">
-        <v>42</v>
-      </c>
-      <c r="J28" t="s">
-        <v>61</v>
+        <v>0.00430715491474091</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5621.62603480591</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K28" t="s">
+        <v>44</v>
+      </c>
+      <c r="L28" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-16711.3634303374</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-16687.4269425026</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8359.6817151687</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0000982646535001163</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.00766466973784182</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4687.23420538713</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K29" t="s">
+        <v>44</v>
+      </c>
+      <c r="L29" t="s">
         <v>63</v>
-      </c>
-      <c r="D29" t="n">
-        <v>-17841.2674418593</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-17811.3468320658</v>
-      </c>
-      <c r="F29" t="n">
-        <v>8925.63372092964</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.0000000543050794749149</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.000101047988330443</v>
-      </c>
-      <c r="I29" t="s">
-        <v>42</v>
-      </c>
-      <c r="J29" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D30" t="n">
-        <v>-12618.2868051962</v>
+        <v>-10849.6298936207</v>
       </c>
       <c r="E30" t="n">
-        <v>-12588.3661954027</v>
+        <v>-10825.6934057859</v>
       </c>
       <c r="F30" t="n">
-        <v>6314.14340259809</v>
+        <v>5428.81494681033</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00000999167627594231</v>
+        <v>0.00112544275340769</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00114854170741762</v>
-      </c>
-      <c r="I30" t="s">
-        <v>42</v>
-      </c>
-      <c r="J30" t="s">
-        <v>57</v>
+        <v>0.0243310309199076</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2329.32045369707</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K30" t="s">
+        <v>44</v>
+      </c>
+      <c r="L30" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D31" t="n">
-        <v>-16187.7828771156</v>
+        <v>-13915.8189354138</v>
       </c>
       <c r="E31" t="n">
-        <v>-16157.8622673221</v>
+        <v>-13891.882447579</v>
       </c>
       <c r="F31" t="n">
-        <v>8098.89143855781</v>
+        <v>6961.90946770692</v>
       </c>
       <c r="G31" t="n">
-        <v>0.00000120903592295575</v>
+        <v>0.000377390286559431</v>
       </c>
       <c r="H31" t="n">
-        <v>0.000352339054425865</v>
-      </c>
-      <c r="I31" t="s">
-        <v>42</v>
-      </c>
-      <c r="J31" t="s">
-        <v>57</v>
+        <v>0.0137695685839832</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3216.14075778238</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K31" t="s">
+        <v>44</v>
+      </c>
+      <c r="L31" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-11081.523323752</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-11057.5868359172</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5544.76166187601</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.000556982610417858</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.0171338026248393</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3410.28943382607</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K32" t="s">
+        <v>44</v>
+      </c>
+      <c r="L32" t="s">
         <v>59</v>
-      </c>
-      <c r="D32" t="n">
-        <v>-13905.261927556</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-13875.3413177625</v>
-      </c>
-      <c r="F32" t="n">
-        <v>6957.63096377799</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.00000188332766628651</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.000533514044187929</v>
-      </c>
-      <c r="I32" t="s">
-        <v>42</v>
-      </c>
-      <c r="J32" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D33" t="n">
-        <v>-21907.7870476517</v>
+        <v>-21086.222814587</v>
       </c>
       <c r="E33" t="n">
-        <v>-21871.8823158995</v>
+        <v>-21056.3022047935</v>
       </c>
       <c r="F33" t="n">
-        <v>10959.8935238259</v>
+        <v>10548.1114072935</v>
       </c>
       <c r="G33" t="n">
-        <v>0.00000000264905855532464</v>
+        <v>0.0000221028496511079</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0000199526902019476</v>
-      </c>
-      <c r="I33" t="s">
-        <v>42</v>
-      </c>
-      <c r="J33" t="s">
-        <v>61</v>
+        <v>0.00350398158196061</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6149.66082564719</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K33" t="s">
+        <v>44</v>
+      </c>
+      <c r="L33" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D34" t="n">
-        <v>-22126.0079652002</v>
+        <v>-21446.4359075332</v>
       </c>
       <c r="E34" t="n">
-        <v>-22090.103233448</v>
+        <v>-21416.5152977397</v>
       </c>
       <c r="F34" t="n">
-        <v>11069.0039826001</v>
+        <v>10728.2179537666</v>
       </c>
       <c r="G34" t="n">
-        <v>0.00000000631580908854966</v>
+        <v>0.0000343323132413725</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0000311074353849485</v>
-      </c>
-      <c r="I34" t="s">
-        <v>42</v>
-      </c>
-      <c r="J34" t="s">
-        <v>61</v>
+        <v>0.00431244834374611</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5513.45412415785</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K34" t="s">
+        <v>44</v>
+      </c>
+      <c r="L34" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-17841.2674418593</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-17811.3468320658</v>
+      </c>
+      <c r="F35" t="n">
+        <v>8925.63372092964</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.000097968589463147</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.007610469739582</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4678.15826661324</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K35" t="s">
+        <v>44</v>
+      </c>
+      <c r="L35" t="s">
         <v>63</v>
-      </c>
-      <c r="D35" t="n">
-        <v>-18500.777830922</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-18464.8730991698</v>
-      </c>
-      <c r="F35" t="n">
-        <v>9256.38891546099</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.0000000333883423762622</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.0000903674333894644</v>
-      </c>
-      <c r="I35" t="s">
-        <v>42</v>
-      </c>
-      <c r="J35" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D36" t="n">
-        <v>-13273.652880235</v>
+        <v>-12618.2868051962</v>
       </c>
       <c r="E36" t="n">
-        <v>-13237.7481484828</v>
+        <v>-12588.3661954027</v>
       </c>
       <c r="F36" t="n">
-        <v>6642.82644011749</v>
+        <v>6314.14340259809</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00000878994316463406</v>
+        <v>0.00111656063919218</v>
       </c>
       <c r="H36" t="n">
-        <v>0.001097890616231</v>
-      </c>
-      <c r="I36" t="s">
-        <v>42</v>
-      </c>
-      <c r="J36" t="s">
-        <v>57</v>
+        <v>0.0243001199699729</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2332.57302733221</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K36" t="s">
+        <v>44</v>
+      </c>
+      <c r="L36" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D37" t="n">
-        <v>-16722.1397768847</v>
+        <v>-16187.7828771156</v>
       </c>
       <c r="E37" t="n">
-        <v>-16686.2350451324</v>
+        <v>-16157.8622673221</v>
       </c>
       <c r="F37" t="n">
-        <v>8367.06988844233</v>
+        <v>8098.89143855781</v>
       </c>
       <c r="G37" t="n">
-        <v>0.00000120517161392212</v>
+        <v>0.00035741869281663</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00033832332513122</v>
-      </c>
-      <c r="I37" t="s">
-        <v>42</v>
-      </c>
-      <c r="J37" t="s">
-        <v>57</v>
+        <v>0.0133076321689625</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3392.31545946402</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K37" t="s">
+        <v>44</v>
+      </c>
+      <c r="L37" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-13905.261927556</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-13875.3413177625</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6957.63096377799</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.000497409451221445</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0158462756380001</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3642.44767713648</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K38" t="s">
+        <v>44</v>
+      </c>
+      <c r="L38" t="s">
         <v>59</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-14493.4589158028</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-14457.5541840505</v>
-      </c>
-      <c r="F38" t="n">
-        <v>7252.72945790138</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.0000016802505525463</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.00046493175177366</v>
-      </c>
-      <c r="I38" t="s">
-        <v>42</v>
-      </c>
-      <c r="J38" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D39" t="n">
-        <v>-20390.7246340714</v>
+        <v>-21219.4284734558</v>
       </c>
       <c r="E39" t="n">
-        <v>-20354.8199023192</v>
+        <v>-21183.5237417036</v>
       </c>
       <c r="F39" t="n">
-        <v>10201.3623170357</v>
+        <v>10615.7142367279</v>
       </c>
       <c r="G39" t="n">
-        <v>0.00000000287231289027716</v>
+        <v>0.000022072815914142</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0000220725090305658</v>
-      </c>
-      <c r="I39" t="s">
-        <v>42</v>
-      </c>
-      <c r="J39" t="s">
-        <v>61</v>
+        <v>0.00350164442843429</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6197.99496720381</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K39" t="s">
+        <v>44</v>
+      </c>
+      <c r="L39" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>-20663.0629217926</v>
+        <v>-21922.1562477529</v>
       </c>
       <c r="E40" t="n">
-        <v>-20627.1581900404</v>
+        <v>-21886.2515160007</v>
       </c>
       <c r="F40" t="n">
-        <v>10337.5314608963</v>
+        <v>10967.0781238764</v>
       </c>
       <c r="G40" t="n">
-        <v>0.00000000684221974618736</v>
+        <v>0.0000343548762962215</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0000342989225345756</v>
-      </c>
-      <c r="I40" t="s">
-        <v>42</v>
-      </c>
-      <c r="J40" t="s">
-        <v>61</v>
+        <v>0.00431465842523526</v>
+      </c>
+      <c r="I40" t="n">
+        <v>5906.117566007</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K40" t="s">
+        <v>44</v>
+      </c>
+      <c r="L40" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C41" t="s">
+        <v>65</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-17933.4795528587</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-17897.5748211065</v>
+      </c>
+      <c r="F41" t="n">
+        <v>8972.73977642934</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.0000982091782302409</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.00764416773516557</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4798.44491601081</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K41" t="s">
+        <v>44</v>
+      </c>
+      <c r="L41" t="s">
         <v>63</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-17296.0175829807</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-17260.1128512285</v>
-      </c>
-      <c r="F41" t="n">
-        <v>8654.00879149036</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.000000041989390640004</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.0000979222749789158</v>
-      </c>
-      <c r="I41" t="s">
-        <v>42</v>
-      </c>
-      <c r="J41" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D42" t="n">
-        <v>-11957.8877932379</v>
+        <v>-13272.5886735945</v>
       </c>
       <c r="E42" t="n">
-        <v>-11921.9830614857</v>
+        <v>-13236.6839418423</v>
       </c>
       <c r="F42" t="n">
-        <v>5984.94389661896</v>
+        <v>6642.29433679725</v>
       </c>
       <c r="G42" t="n">
-        <v>0.00000884643765804399</v>
+        <v>0.00111535057972973</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00111799097086115</v>
-      </c>
-      <c r="I42" t="s">
-        <v>42</v>
-      </c>
-      <c r="J42" t="s">
-        <v>57</v>
+        <v>0.0242942022583521</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-1966.83762194394</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K42" t="s">
+        <v>44</v>
+      </c>
+      <c r="L42" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D43" t="n">
-        <v>-15439.990288026</v>
+        <v>-16714.5673553433</v>
       </c>
       <c r="E43" t="n">
-        <v>-15404.0855562738</v>
+        <v>-16678.6626235911</v>
       </c>
       <c r="F43" t="n">
-        <v>7725.99514401299</v>
+        <v>8363.28367767167</v>
       </c>
       <c r="G43" t="n">
-        <v>0.00000123092826164175</v>
+        <v>0.000357637317046423</v>
       </c>
       <c r="H43" t="n">
-        <v>0.000357952396258783</v>
-      </c>
-      <c r="I43" t="s">
-        <v>42</v>
-      </c>
-      <c r="J43" t="s">
-        <v>57</v>
+        <v>0.0133030522984476</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3098.86926143932</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K43" t="s">
+        <v>44</v>
+      </c>
+      <c r="L43" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-14011.7133296657</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-13975.8085979135</v>
+      </c>
+      <c r="F44" t="n">
+        <v>7011.85666483284</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.000498531039874012</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.0158658956528862</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3730.59330557494</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K44" t="s">
+        <v>44</v>
+      </c>
+      <c r="L44" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" t="s">
+        <v>61</v>
+      </c>
+      <c r="D45" t="n">
+        <v>635.787255489474</v>
+      </c>
+      <c r="E45" t="n">
+        <v>671.691987241692</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-311.893627744737</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.0340401235620799</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.136455701792049</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5671.74571879526</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K45" t="s">
+        <v>44</v>
+      </c>
+      <c r="L45" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
         <v>33</v>
       </c>
-      <c r="B44" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B46" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" t="s">
+        <v>62</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-20390.7246340714</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-20354.8199023192</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10201.3623170357</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0000220758286778471</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.00350031624878505</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-1853.31135892352</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K46" t="s">
+        <v>44</v>
+      </c>
+      <c r="L46" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="B47" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" t="s">
+        <v>64</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-20663.0629217926</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-20627.1581900404</v>
+      </c>
+      <c r="F47" t="n">
+        <v>10337.5314608963</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.000034504478514368</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.00431956984664171</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-1016.93395371286</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K47" t="s">
+        <v>44</v>
+      </c>
+      <c r="L47" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" t="s">
+        <v>65</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-17296.0175829807</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-17260.1128512285</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8654.00879149036</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0000985472216988258</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.00768022841340114</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-3545.68147052504</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K48" t="s">
+        <v>44</v>
+      </c>
+      <c r="L48" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-11957.8877932379</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-11921.9830614857</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5984.94389661896</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.00111469686403829</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.0242335941397127</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-5089.93719689648</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K49" t="s">
+        <v>44</v>
+      </c>
+      <c r="L49" t="s">
         <v>59</v>
       </c>
-      <c r="D44" t="n">
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-15439.990288026</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-15404.0855562738</v>
+      </c>
+      <c r="F50" t="n">
+        <v>7725.99514401299</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.000360581716372196</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.0133492730468956</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-4542.62407350342</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K50" t="s">
+        <v>44</v>
+      </c>
+      <c r="L50" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>33</v>
+      </c>
+      <c r="B51" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" t="n">
         <v>-13205.7862971612</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E51" t="n">
         <v>-13169.881565409</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F51" t="n">
         <v>6608.89314858061</v>
       </c>
-      <c r="G44" t="n">
-        <v>0.00000174735334722701</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.000497048601037352</v>
-      </c>
-      <c r="I44" t="s">
-        <v>42</v>
-      </c>
-      <c r="J44" t="s">
-        <v>57</v>
+      <c r="G51" t="n">
+        <v>0.000499332857659875</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.0158667054091025</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-4678.11138575108</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K51" t="s">
+        <v>44</v>
+      </c>
+      <c r="L51" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2456,10 +3101,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
         <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>65</v>
       </c>
       <c r="C1" t="s">
         <v>66</v>
@@ -2473,65 +3118,100 @@
       <c r="F1" t="s">
         <v>69</v>
       </c>
+      <c r="G1" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.015625</v>
       </c>
-      <c r="E2" t="b">
+      <c r="F2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
-        <v>71</v>
+      <c r="G2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="n">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0.015625</v>
       </c>
-      <c r="E3" t="b">
+      <c r="F3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
-        <v>71</v>
+      <c r="G3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="n">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0.015625</v>
       </c>
-      <c r="E4" t="b">
+      <c r="F4" t="b">
         <v>1</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
         <v>71</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2547,115 +3227,115 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
         <v>19</v>
       </c>
       <c r="D1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" t="s">
         <v>41</v>
       </c>
-      <c r="G1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" t="s">
-        <v>39</v>
-      </c>
       <c r="I1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00000414024747420764</v>
+        <v>0.00323211218233967</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00000181534050675676</v>
+        <v>0.000499332857659875</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000661946353277147</v>
+        <v>0.0270812965002393</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000515281322612641</v>
+        <v>0.0158667054091025</v>
       </c>
       <c r="H2" t="n">
-        <v>-13637.6016428335</v>
+        <v>-12501.926941861</v>
       </c>
       <c r="I2" t="n">
-        <v>-13589.4574038955</v>
+        <v>-13272.5886735945</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>6.65327515839989</v>
+        <v>486077125061657311406804468608466688004288482220686066204280642282482228606842022426646262024420288666048062864086884266268600040884262404</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00124899041651523</v>
+        <v>3.51076521992263</v>
       </c>
       <c r="F3" t="n">
-        <v>0.176305690514384</v>
+        <v>16692064204806005671086460048040022062646604864880668620406624266040</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0232603534794983</v>
+        <v>0.411565100315132</v>
       </c>
       <c r="H3" t="n">
-        <v>-16247.1220832456</v>
+        <v>-12501.926941861</v>
       </c>
       <c r="I3" t="n">
-        <v>-21048.5697816639</v>
+        <v>-13272.5886735945</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000000184438433676003</v>
+        <v>0.0000515696837151099</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0000000065987863046012</v>
+        <v>0.000034343594768797</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0000507696252323996</v>
+        <v>0.00515505114745629</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0000339667352763216</v>
+        <v>0.00431355338449069</v>
       </c>
       <c r="H4" t="n">
-        <v>-19786.3680996553</v>
+        <v>-19664.7423855131</v>
       </c>
       <c r="I4" t="n">
         <v>-20242.3539394943</v>
@@ -2663,31 +3343,31 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0000454283345482919</v>
+        <v>501514667358122094644268048</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000033297307957778</v>
+        <v>0.13202578770666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00510518799494098</v>
+        <v>1532873946776.21</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00451548259175802</v>
+        <v>0.135543860456709</v>
       </c>
       <c r="H5" t="n">
-        <v>-31388.1151565577</v>
+        <v>-19664.7423855131</v>
       </c>
       <c r="I5" t="n">
-        <v>-32326.2491294199</v>
+        <v>-20242.3539394943</v>
       </c>
     </row>
   </sheetData>
@@ -2703,24 +3383,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -2731,10 +3411,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>

--- a/results/consolidated/NF_vs_Standard_GARCH_Comparison.xlsx
+++ b/results/consolidated/NF_vs_Standard_GARCH_Comparison.xlsx
@@ -36,13 +36,13 @@
     <t xml:space="preserve">Overall mean MSE - Standard</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52760105032062e+137</t>
+    <t xml:space="preserve">0.000370314488142505</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean MSE - NF-GARCH</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00170545178299988</t>
+    <t xml:space="preserve">0.000364682226386018</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean AIC - Standard</t>
@@ -57,13 +57,13 @@
     <t xml:space="preserve">NF-GARCH wins (lower MSE)</t>
   </si>
   <si>
-    <t xml:space="preserve">24</t>
+    <t xml:space="preserve">19</t>
   </si>
   <si>
     <t xml:space="preserve">Standard GARCH wins (lower MSE)</t>
   </si>
   <si>
-    <t xml:space="preserve">1</t>
+    <t xml:space="preserve">6</t>
   </si>
   <si>
     <t xml:space="preserve">Overall winner</t>
@@ -737,16 +737,16 @@
         <v>-16456.3401877928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000354956494493567</v>
+        <v>0.000354965353094005</v>
       </c>
       <c r="I2" t="n">
-        <v>59443726319534449280006002206028424662</v>
+        <v>0.000359327085896616</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0114916145174231</v>
+        <v>0.0114919689675483</v>
       </c>
       <c r="K2" t="n">
-        <v>495480725121196672</v>
+        <v>0.0116041972925204</v>
       </c>
       <c r="L2" t="n">
         <v>8252.12245977249</v>
@@ -758,10 +758,10 @@
         <v>-0.0000000000109139364212751</v>
       </c>
       <c r="O2" t="n">
-        <v>100</v>
+        <v>1.21386140199458</v>
       </c>
       <c r="P2" t="n">
-        <v>100</v>
+        <v>0.967135616045136</v>
       </c>
     </row>
     <row r="3">
@@ -787,16 +787,16 @@
         <v>671.691987241692</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0340401235620799</v>
+        <v>0.000507650148030649</v>
       </c>
       <c r="I3" t="n">
-        <v>6319002625801544635622286848826426420822064026860400222086266606486846066284682406648224486460668628846026024882080400848446860806626608662</v>
+        <v>0.000650594630148603</v>
       </c>
       <c r="J3" t="n">
-        <v>0.136455701792049</v>
+        <v>0.0161296690515369</v>
       </c>
       <c r="K3" t="n">
-        <v>216996834662478079722482026088480064066884602844262466420888604862226</v>
+        <v>0.0188741769339226</v>
       </c>
       <c r="L3" t="n">
         <v>-311.893627744737</v>
@@ -808,10 +808,10 @@
         <v>0.000000000000227373675443232</v>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
+        <v>21.9713590450791</v>
       </c>
       <c r="P3" t="n">
-        <v>100</v>
+        <v>14.5410731921929</v>
       </c>
     </row>
     <row r="4">
@@ -837,16 +837,16 @@
         <v>-17476.4175403596</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000354359301181795</v>
+        <v>0.000354121096211184</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004457363014615</v>
+        <v>0.000355250787807204</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0114872701330868</v>
+        <v>0.0114829136709332</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0126079045451664</v>
+        <v>0.0115059567174912</v>
       </c>
       <c r="L4" t="n">
         <v>8762.1611360559</v>
@@ -858,10 +858,10 @@
         <v>-0.00000000000363797880709171</v>
       </c>
       <c r="O4" t="n">
-        <v>20.5002374677796</v>
+        <v>0.317998336609745</v>
       </c>
       <c r="P4" t="n">
-        <v>8.88834784610695</v>
+        <v>0.200270582653854</v>
       </c>
     </row>
     <row r="5">
@@ -887,16 +887,16 @@
         <v>-15313.5777125072</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000369080617213171</v>
+        <v>0.00037150952613407</v>
       </c>
       <c r="I5" t="n">
-        <v>3.29130484982847</v>
+        <v>0.000364336427127678</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0117845885225423</v>
+        <v>0.0118346604055098</v>
       </c>
       <c r="K5" t="n">
-        <v>0.317372015862975</v>
+        <v>0.0117739750196379</v>
       </c>
       <c r="L5" t="n">
         <v>7672.757100171</v>
@@ -908,10 +908,10 @@
         <v>0.00000000000909494701772928</v>
       </c>
       <c r="O5" t="n">
-        <v>99.9887861916762</v>
+        <v>-1.96881192005481</v>
       </c>
       <c r="P5" t="n">
-        <v>96.2868217947639</v>
+        <v>-0.515419692760528</v>
       </c>
     </row>
     <row r="6">
@@ -937,16 +937,16 @@
         <v>-17150.9556858477</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00035429875593098</v>
+        <v>0.00035430494316404</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5559196884804</v>
+        <v>0.000355630294737505</v>
       </c>
       <c r="J6" t="n">
-        <v>0.011480154573704</v>
+        <v>0.0114778767998602</v>
       </c>
       <c r="K6" t="n">
-        <v>0.205412486841088</v>
+        <v>0.0114975593164883</v>
       </c>
       <c r="L6" t="n">
         <v>8595.43814782061</v>
@@ -958,10 +958,10 @@
         <v>0.00000000000363797880709171</v>
       </c>
       <c r="O6" t="n">
-        <v>99.9900363678888</v>
+        <v>0.372676791903827</v>
       </c>
       <c r="P6" t="n">
-        <v>94.4111700557983</v>
+        <v>0.171188650446507</v>
       </c>
     </row>
   </sheetData>
@@ -1003,10 +1003,10 @@
         <v>-15940.078354814</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00170545178299988</v>
+        <v>0.000364682226386018</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0165566987309035</v>
+        <v>0.0117541675245858</v>
       </c>
     </row>
     <row r="3">
@@ -1020,10 +1020,10 @@
         <v>-15940.078354814</v>
       </c>
       <c r="D3" t="n">
-        <v>252760105032061765680848840286000462602800260064088682068208860286084808404608640882402804864864222028224468086444628226428480862442486848</v>
+        <v>0.000370314488142505</v>
       </c>
       <c r="E3" t="n">
-        <v>8679873386499122659400606262886664840246688000868226606248880602082</v>
+        <v>0.01188657228043</v>
       </c>
     </row>
   </sheetData>
@@ -1065,10 +1065,10 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -1099,10 +1099,10 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>83.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -1116,10 +1116,10 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -1208,13 +1208,13 @@
         <v>5428.81494681033</v>
       </c>
       <c r="G2" t="n">
-        <v>0.601409767741544</v>
+        <v>0.00113294191660519</v>
       </c>
       <c r="H2" t="n">
-        <v>0.252193599528106</v>
+        <v>0.0247395278593571</v>
       </c>
       <c r="I2" t="n">
-        <v>5270.53498430595</v>
+        <v>3088.98175011407</v>
       </c>
       <c r="J2" t="n">
         <v>1000</v>
@@ -1246,13 +1246,13 @@
         <v>6314.14340259809</v>
       </c>
       <c r="G3" t="n">
-        <v>20.3333406429236</v>
+        <v>0.00111798915874502</v>
       </c>
       <c r="H3" t="n">
-        <v>0.620988161819819</v>
+        <v>0.0242360232260632</v>
       </c>
       <c r="I3" t="n">
-        <v>5038.99852606956</v>
+        <v>3082.38296453631</v>
       </c>
       <c r="J3" t="n">
         <v>1000</v>
@@ -1284,13 +1284,13 @@
         <v>5984.94389661896</v>
       </c>
       <c r="G4" t="n">
-        <v>33659430548004201794266822262</v>
+        <v>0.00112990698547962</v>
       </c>
       <c r="H4" t="n">
-        <v>20990175346511.8</v>
+        <v>0.0245719942992481</v>
       </c>
       <c r="I4" t="n">
-        <v>179.702416351401</v>
+        <v>2802.74463200126</v>
       </c>
       <c r="J4" t="n">
         <v>1000</v>
@@ -1322,13 +1322,13 @@
         <v>6642.29433679725</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00111720183913927</v>
+        <v>0.00111747661996816</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0243034240346594</v>
+        <v>0.0242999039203381</v>
       </c>
       <c r="I5" t="n">
-        <v>3115.10876424277</v>
+        <v>3121.93810844537</v>
       </c>
       <c r="J5" t="n">
         <v>1000</v>
@@ -1360,13 +1360,13 @@
         <v>6961.90946770692</v>
       </c>
       <c r="G6" t="n">
-        <v>8.13263734830384</v>
+        <v>0.000359184098439669</v>
       </c>
       <c r="H6" t="n">
-        <v>0.470386080763109</v>
+        <v>0.0134236857455301</v>
       </c>
       <c r="I6" t="n">
-        <v>6035.84043645253</v>
+        <v>4072.64640433012</v>
       </c>
       <c r="J6" t="n">
         <v>1000</v>
@@ -1398,13 +1398,13 @@
         <v>8098.89143855781</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0269172399176276</v>
+        <v>0.000357935371424075</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0561841775044956</v>
+        <v>0.0133258371224686</v>
       </c>
       <c r="I7" t="n">
-        <v>5947.46170065369</v>
+        <v>4056.03865678739</v>
       </c>
       <c r="J7" t="n">
         <v>1000</v>
@@ -1436,13 +1436,13 @@
         <v>7725.99514401299</v>
       </c>
       <c r="G8" t="n">
-        <v>356662357876333763744642020668642422202</v>
+        <v>0.000357590756871472</v>
       </c>
       <c r="H8" t="n">
-        <v>2972835482014035968</v>
+        <v>0.013311453571699</v>
       </c>
       <c r="I8" t="n">
-        <v>265.831597174635</v>
+        <v>3511.61540514467</v>
       </c>
       <c r="J8" t="n">
         <v>1000</v>
@@ -1474,13 +1474,13 @@
         <v>8363.28367767167</v>
       </c>
       <c r="G9" t="n">
-        <v>0.000357626028317543</v>
+        <v>0.000357804248483678</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0133198188840382</v>
+        <v>0.0133199728861673</v>
       </c>
       <c r="I9" t="n">
-        <v>4094.40631066088</v>
+        <v>4083.35768178638</v>
       </c>
       <c r="J9" t="n">
         <v>1000</v>
@@ -1512,13 +1512,13 @@
         <v>5544.76166187601</v>
       </c>
       <c r="G10" t="n">
-        <v>3.51076521992263</v>
+        <v>0.000539147728467235</v>
       </c>
       <c r="H10" t="n">
-        <v>0.411565100315132</v>
+        <v>0.0170295164322842</v>
       </c>
       <c r="I10" t="n">
-        <v>5538.70650814066</v>
+        <v>3715.40733591235</v>
       </c>
       <c r="J10" t="n">
         <v>1000</v>
@@ -1550,13 +1550,13 @@
         <v>6957.63096377799</v>
       </c>
       <c r="G11" t="n">
-        <v>0.366918678159065</v>
+        <v>0.00050213825635879</v>
       </c>
       <c r="H11" t="n">
-        <v>0.163903114402675</v>
+        <v>0.0159104144455574</v>
       </c>
       <c r="I11" t="n">
-        <v>5678.53245618295</v>
+        <v>3753.97980583106</v>
       </c>
       <c r="J11" t="n">
         <v>1000</v>
@@ -1588,13 +1588,13 @@
         <v>-311.893627744737</v>
       </c>
       <c r="G12" t="n">
-        <v>6319002625801544635622286848826426420822064026860400222086266606486846066284682406648224486460668628846026024882080400848446860806626608662</v>
+        <v>0.000650594630148603</v>
       </c>
       <c r="H12" t="n">
-        <v>216996834662478079722482026088480064066884602844262466420888604862226</v>
+        <v>0.0188741769339226</v>
       </c>
       <c r="I12" t="n">
-        <v>7510.19102579582</v>
+        <v>4691.64115301535</v>
       </c>
       <c r="J12" t="n">
         <v>1000</v>
@@ -1626,13 +1626,13 @@
         <v>6608.89314858061</v>
       </c>
       <c r="G13" t="n">
-        <v>1195319065165623506266802266</v>
+        <v>0.000512966953772271</v>
       </c>
       <c r="H13" t="n">
-        <v>9484050436284.61</v>
+        <v>0.0162197665776192</v>
       </c>
       <c r="I13" t="n">
-        <v>100.531728338937</v>
+        <v>3672.72176974805</v>
       </c>
       <c r="J13" t="n">
         <v>1000</v>
@@ -1664,13 +1664,13 @@
         <v>7011.85666483284</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000544228252986239</v>
+        <v>0.000500956539412569</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0168477859626725</v>
+        <v>0.0159139676634201</v>
       </c>
       <c r="I14" t="n">
-        <v>4100.46093900027</v>
+        <v>3797.41220461032</v>
       </c>
       <c r="J14" t="n">
         <v>1000</v>
@@ -1702,13 +1702,13 @@
         <v>9690.38318700543</v>
       </c>
       <c r="G15" t="n">
-        <v>7.39654709151959</v>
+        <v>0.0000220213340041746</v>
       </c>
       <c r="H15" t="n">
-        <v>0.593515941331431</v>
+        <v>0.00350095176524737</v>
       </c>
       <c r="I15" t="n">
-        <v>7795.02636457378</v>
+        <v>6012.85300157449</v>
       </c>
       <c r="J15" t="n">
         <v>1000</v>
@@ -1740,13 +1740,13 @@
         <v>10548.1114072935</v>
       </c>
       <c r="G16" t="n">
-        <v>0.182363083709309</v>
+        <v>0.0000222061640547421</v>
       </c>
       <c r="H16" t="n">
-        <v>0.156067440893827</v>
+        <v>0.00351686828601548</v>
       </c>
       <c r="I16" t="n">
-        <v>7829.68128972402</v>
+        <v>6015.25647204138</v>
       </c>
       <c r="J16" t="n">
         <v>1000</v>
@@ -1778,13 +1778,13 @@
         <v>10201.3623170357</v>
       </c>
       <c r="G17" t="n">
-        <v>5020070539752685951688286862</v>
+        <v>0.0000224197509651795</v>
       </c>
       <c r="H17" t="n">
-        <v>13010544887916.1</v>
+        <v>0.00353001868559982</v>
       </c>
       <c r="I17" t="n">
-        <v>2040.23721636389</v>
+        <v>5813.5892136715</v>
       </c>
       <c r="J17" t="n">
         <v>1000</v>
@@ -1816,13 +1816,13 @@
         <v>10615.7142367279</v>
       </c>
       <c r="G18" t="n">
-        <v>0.000287481693506639</v>
+        <v>0.0000223025315142103</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00618474393245327</v>
+        <v>0.003526554845791</v>
       </c>
       <c r="I18" t="n">
-        <v>6539.2203797</v>
+        <v>6069.33631543247</v>
       </c>
       <c r="J18" t="n">
         <v>1000</v>
@@ -1854,13 +1854,13 @@
         <v>10050.9916224586</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0434668026779057</v>
+        <v>0.0000345281255929013</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0615510932204801</v>
+        <v>0.00432834545135828</v>
       </c>
       <c r="I19" t="n">
-        <v>7536.74279232573</v>
+        <v>5791.65063407992</v>
       </c>
       <c r="J19" t="n">
         <v>1000</v>
@@ -1892,13 +1892,13 @@
         <v>10728.2179537666</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0816884917040117</v>
+        <v>0.0000347876795851249</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0581959240540824</v>
+        <v>0.00433715731224581</v>
       </c>
       <c r="I20" t="n">
-        <v>7639.43295754841</v>
+        <v>5788.61400563658</v>
       </c>
       <c r="J20" t="n">
         <v>1000</v>
@@ -1930,13 +1930,13 @@
         <v>10337.5314608963</v>
       </c>
       <c r="G21" t="n">
-        <v>997999452034110633222806668</v>
+        <v>0.0000348409539833613</v>
       </c>
       <c r="H21" t="n">
-        <v>5323836690529.1</v>
+        <v>0.00437363167074261</v>
       </c>
       <c r="I21" t="n">
-        <v>1669.3534648896</v>
+        <v>5385.07082728935</v>
       </c>
       <c r="J21" t="n">
         <v>1000</v>
@@ -1968,13 +1968,13 @@
         <v>10967.0781238764</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0000344080730827349</v>
+        <v>0.0000343941137794673</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00432211437089372</v>
+        <v>0.00431737160015301</v>
       </c>
       <c r="I22" t="n">
-        <v>5911.81214850415</v>
+        <v>5885.93095731669</v>
       </c>
       <c r="J22" t="n">
         <v>1000</v>
@@ -2006,13 +2006,13 @@
         <v>8359.6817151687</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0630028688052877</v>
+        <v>0.0000981953596569056</v>
       </c>
       <c r="H23" t="n">
-        <v>0.115020280019591</v>
+        <v>0.00762182286405039</v>
       </c>
       <c r="I23" t="n">
-        <v>6675.6358360275</v>
+        <v>4931.81945937339</v>
       </c>
       <c r="J23" t="n">
         <v>1000</v>
@@ -2044,13 +2044,13 @@
         <v>8925.63372092964</v>
       </c>
       <c r="G24" t="n">
-        <v>0.344289994468813</v>
+        <v>0.0000987251382572782</v>
       </c>
       <c r="H24" t="n">
-        <v>0.177136102371628</v>
+        <v>0.00765905550657954</v>
       </c>
       <c r="I24" t="n">
-        <v>6640.61148047267</v>
+        <v>4936.37270852313</v>
       </c>
       <c r="J24" t="n">
         <v>1000</v>
@@ -2082,13 +2082,13 @@
         <v>8654.00879149036</v>
       </c>
       <c r="G25" t="n">
-        <v>106016510668686311296088</v>
+        <v>0.0000982371143077934</v>
       </c>
       <c r="H25" t="n">
-        <v>60105782868.1831</v>
+        <v>0.00761831895021398</v>
       </c>
       <c r="I25" t="n">
-        <v>1564.83509158342</v>
+        <v>4400.65794643772</v>
       </c>
       <c r="J25" t="n">
         <v>1000</v>
@@ -2120,13 +2120,13 @@
         <v>8972.73977642934</v>
       </c>
       <c r="G26" t="n">
-        <v>0.000333471921736581</v>
+        <v>0.0000985706736851411</v>
       </c>
       <c r="H26" t="n">
-        <v>0.010669540086281</v>
+        <v>0.00765796938907799</v>
       </c>
       <c r="I26" t="n">
-        <v>5310.20657263366</v>
+        <v>4968.38507439652</v>
       </c>
       <c r="J26" t="n">
         <v>1000</v>
@@ -2158,13 +2158,13 @@
         <v>9690.38318700543</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0000221142231310187</v>
+        <v>0.0000221586308442225</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00350130435394098</v>
+        <v>0.00350657522709918</v>
       </c>
       <c r="I27" t="n">
-        <v>6150.84566075275</v>
+        <v>6091.12355668695</v>
       </c>
       <c r="J27" t="n">
         <v>1000</v>
@@ -2196,13 +2196,13 @@
         <v>10050.9916224586</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0000342891762629105</v>
+        <v>0.000034380430021123</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00430715491474091</v>
+        <v>0.00431437218736813</v>
       </c>
       <c r="I28" t="n">
-        <v>5621.62603480591</v>
+        <v>5568.48559558248</v>
       </c>
       <c r="J28" t="n">
         <v>1000</v>
@@ -2234,13 +2234,13 @@
         <v>8359.6817151687</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0000982646535001163</v>
+        <v>0.0000985129890248958</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00766466973784182</v>
+        <v>0.00767487245432214</v>
       </c>
       <c r="I29" t="n">
-        <v>4687.23420538713</v>
+        <v>4597.28223830732</v>
       </c>
       <c r="J29" t="n">
         <v>1000</v>
@@ -2272,13 +2272,13 @@
         <v>5428.81494681033</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00112544275340769</v>
+        <v>0.00112886449992447</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0243310309199076</v>
+        <v>0.0243657221470333</v>
       </c>
       <c r="I30" t="n">
-        <v>2329.32045369707</v>
+        <v>2332.45241615951</v>
       </c>
       <c r="J30" t="n">
         <v>1000</v>
@@ -2310,13 +2310,13 @@
         <v>6961.90946770692</v>
       </c>
       <c r="G31" t="n">
-        <v>0.000377390286559431</v>
+        <v>0.000380234698186531</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0137695685839832</v>
+        <v>0.0138347283150291</v>
       </c>
       <c r="I31" t="n">
-        <v>3216.14075778238</v>
+        <v>3328.66132101524</v>
       </c>
       <c r="J31" t="n">
         <v>1000</v>
@@ -2348,13 +2348,13 @@
         <v>5544.76166187601</v>
       </c>
       <c r="G32" t="n">
-        <v>0.000556982610417858</v>
+        <v>0.000564905908803178</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0171338026248393</v>
+        <v>0.0173116921022071</v>
       </c>
       <c r="I32" t="n">
-        <v>3410.28943382607</v>
+        <v>3298.7086956953</v>
       </c>
       <c r="J32" t="n">
         <v>1000</v>
@@ -2386,13 +2386,13 @@
         <v>10548.1114072935</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0000221028496511079</v>
+        <v>0.0000221125950961247</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00350398158196061</v>
+        <v>0.00350258090010257</v>
       </c>
       <c r="I33" t="n">
-        <v>6149.66082564719</v>
+        <v>6126.97657444797</v>
       </c>
       <c r="J33" t="n">
         <v>1000</v>
@@ -2424,13 +2424,13 @@
         <v>10728.2179537666</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0000343323132413725</v>
+        <v>0.0000343134264060025</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00431244834374611</v>
+        <v>0.00431232536809715</v>
       </c>
       <c r="I34" t="n">
-        <v>5513.45412415785</v>
+        <v>5499.50128709555</v>
       </c>
       <c r="J34" t="n">
         <v>1000</v>
@@ -2462,13 +2462,13 @@
         <v>8925.63372092964</v>
       </c>
       <c r="G35" t="n">
-        <v>0.000097968589463147</v>
+        <v>0.000097933010840291</v>
       </c>
       <c r="H35" t="n">
-        <v>0.007610469739582</v>
+        <v>0.00761151151521311</v>
       </c>
       <c r="I35" t="n">
-        <v>4678.15826661324</v>
+        <v>4578.68296307645</v>
       </c>
       <c r="J35" t="n">
         <v>1000</v>
@@ -2500,13 +2500,13 @@
         <v>6314.14340259809</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00111656063919218</v>
+        <v>0.00111465389466928</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0243001199699729</v>
+        <v>0.0242801108181927</v>
       </c>
       <c r="I36" t="n">
-        <v>2332.57302733221</v>
+        <v>2405.97318948381</v>
       </c>
       <c r="J36" t="n">
         <v>1000</v>
@@ -2538,13 +2538,13 @@
         <v>8098.89143855781</v>
       </c>
       <c r="G37" t="n">
-        <v>0.00035741869281663</v>
+        <v>0.000357254897325573</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0133076321689625</v>
+        <v>0.013288167989599</v>
       </c>
       <c r="I37" t="n">
-        <v>3392.31545946402</v>
+        <v>3574.65152851914</v>
       </c>
       <c r="J37" t="n">
         <v>1000</v>
@@ -2576,13 +2576,13 @@
         <v>6957.63096377799</v>
       </c>
       <c r="G38" t="n">
-        <v>0.000497409451221445</v>
+        <v>0.000499561834646966</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0158462756380001</v>
+        <v>0.0158725642079564</v>
       </c>
       <c r="I38" t="n">
-        <v>3642.44767713648</v>
+        <v>3534.88880870559</v>
       </c>
       <c r="J38" t="n">
         <v>1000</v>
@@ -2614,13 +2614,13 @@
         <v>10615.7142367279</v>
       </c>
       <c r="G39" t="n">
-        <v>0.000022072815914142</v>
+        <v>0.0000220734883384139</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00350164442843429</v>
+        <v>0.0034986759293063</v>
       </c>
       <c r="I39" t="n">
-        <v>6197.99496720381</v>
+        <v>6236.36806595074</v>
       </c>
       <c r="J39" t="n">
         <v>1000</v>
@@ -2652,13 +2652,13 @@
         <v>10967.0781238764</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0000343548762962215</v>
+        <v>0.0000342879023770953</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00431465842523526</v>
+        <v>0.00430993310253984</v>
       </c>
       <c r="I40" t="n">
-        <v>5906.117566007</v>
+        <v>5898.69094610072</v>
       </c>
       <c r="J40" t="n">
         <v>1000</v>
@@ -2690,13 +2690,13 @@
         <v>8972.73977642934</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0000982091782302409</v>
+        <v>0.0000978526990960806</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00764416773516557</v>
+        <v>0.00761288363878511</v>
       </c>
       <c r="I41" t="n">
-        <v>4798.44491601081</v>
+        <v>4844.06105502113</v>
       </c>
       <c r="J41" t="n">
         <v>1000</v>
@@ -2728,13 +2728,13 @@
         <v>6642.29433679725</v>
       </c>
       <c r="G42" t="n">
-        <v>0.00111535057972973</v>
+        <v>0.00111522983045958</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0242942022583521</v>
+        <v>0.0243041801407263</v>
       </c>
       <c r="I42" t="n">
-        <v>-1966.83762194394</v>
+        <v>-2036.78567964723</v>
       </c>
       <c r="J42" t="n">
         <v>1000</v>
@@ -2766,13 +2766,13 @@
         <v>8363.28367767167</v>
       </c>
       <c r="G43" t="n">
-        <v>0.000357637317046423</v>
+        <v>0.000357676173393736</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0133030522984476</v>
+        <v>0.0133166881652794</v>
       </c>
       <c r="I43" t="n">
-        <v>3098.86926143932</v>
+        <v>3041.55719520702</v>
       </c>
       <c r="J43" t="n">
         <v>1000</v>
@@ -2804,13 +2804,13 @@
         <v>7011.85666483284</v>
       </c>
       <c r="G44" t="n">
-        <v>0.000498531039874012</v>
+        <v>0.0004976064836022</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0158658956528862</v>
+        <v>0.0158551210489624</v>
       </c>
       <c r="I44" t="n">
-        <v>3730.59330557494</v>
+        <v>3721.83023101062</v>
       </c>
       <c r="J44" t="n">
         <v>1000</v>
@@ -2842,13 +2842,13 @@
         <v>-311.893627744737</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0340401235620799</v>
+        <v>0.000507650148030649</v>
       </c>
       <c r="H45" t="n">
-        <v>0.136455701792049</v>
+        <v>0.0161296690515369</v>
       </c>
       <c r="I45" t="n">
-        <v>5671.74571879526</v>
+        <v>3535.2605011815</v>
       </c>
       <c r="J45" t="n">
         <v>1000</v>
@@ -2880,13 +2880,13 @@
         <v>10201.3623170357</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0000220758286778471</v>
+        <v>0.0000220780623595792</v>
       </c>
       <c r="H46" t="n">
-        <v>0.00350031624878505</v>
+        <v>0.00350005998084207</v>
       </c>
       <c r="I46" t="n">
-        <v>-1853.31135892352</v>
+        <v>-841.128167265488</v>
       </c>
       <c r="J46" t="n">
         <v>1000</v>
@@ -2918,13 +2918,13 @@
         <v>10337.5314608963</v>
       </c>
       <c r="G47" t="n">
-        <v>0.000034504478514368</v>
+        <v>0.00003450217978867</v>
       </c>
       <c r="H47" t="n">
-        <v>0.00431956984664171</v>
+        <v>0.00431935149035112</v>
       </c>
       <c r="I47" t="n">
-        <v>-1016.93395371286</v>
+        <v>-740.941689798181</v>
       </c>
       <c r="J47" t="n">
         <v>1000</v>
@@ -2956,13 +2956,13 @@
         <v>8654.00879149036</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0000985472216988258</v>
+        <v>0.0000985879822252114</v>
       </c>
       <c r="H48" t="n">
-        <v>0.00768022841340114</v>
+        <v>0.00768180191168424</v>
       </c>
       <c r="I48" t="n">
-        <v>-3545.68147052504</v>
+        <v>-2675.00782728108</v>
       </c>
       <c r="J48" t="n">
         <v>1000</v>
@@ -2994,13 +2994,13 @@
         <v>5984.94389661896</v>
       </c>
       <c r="G49" t="n">
-        <v>0.00111469686403829</v>
+        <v>0.001114776146248</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0242335941397127</v>
+        <v>0.0242357836266807</v>
       </c>
       <c r="I49" t="n">
-        <v>-5089.93719689648</v>
+        <v>-5945.51191729431</v>
       </c>
       <c r="J49" t="n">
         <v>1000</v>
@@ -3032,13 +3032,13 @@
         <v>7725.99514401299</v>
       </c>
       <c r="G50" t="n">
-        <v>0.000360581716372196</v>
+        <v>0.000360516319778998</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0133492730468956</v>
+        <v>0.0133480200879298</v>
       </c>
       <c r="I50" t="n">
-        <v>-4542.62407350342</v>
+        <v>-4160.60447744878</v>
       </c>
       <c r="J50" t="n">
         <v>1000</v>
@@ -3070,13 +3070,13 @@
         <v>6608.89314858061</v>
       </c>
       <c r="G51" t="n">
-        <v>0.000499332857659875</v>
+        <v>0.000499331428163572</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0158667054091025</v>
+        <v>0.0158667967078021</v>
       </c>
       <c r="I51" t="n">
-        <v>-4678.11138575108</v>
+        <v>-4888.94348585455</v>
       </c>
       <c r="J51" t="n">
         <v>1000</v>
@@ -3133,13 +3133,13 @@
         <v>71</v>
       </c>
       <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="F2" t="b">
         <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.015625</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
       </c>
       <c r="G2" t="s">
         <v>72</v>
@@ -3179,13 +3179,13 @@
         <v>71</v>
       </c>
       <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="F4" t="b">
         <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.015625</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
       </c>
       <c r="G4" t="s">
         <v>72</v>
@@ -3202,10 +3202,10 @@
         <v>71</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03125</v>
+        <v>0.015625</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -3265,16 +3265,16 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00323211218233967</v>
+        <v>0.000653712481787133</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000499332857659875</v>
+        <v>0.000499561834646966</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0270812965002393</v>
+        <v>0.0178468649545335</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0158667054091025</v>
+        <v>0.0158725642079564</v>
       </c>
       <c r="H2" t="n">
         <v>-12501.926941861</v>
@@ -3294,16 +3294,16 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>486077125061657311406804468608466688004288482220686066204280642282482228606842022426646262024420288666048062864086884266268600040884262404</v>
+        <v>0.000664356404936642</v>
       </c>
       <c r="E3" t="n">
-        <v>3.51076521992263</v>
+        <v>0.000512966953772271</v>
       </c>
       <c r="F3" t="n">
-        <v>16692064204806005671086460048040022062646604864880668620406624266040</v>
+        <v>0.0180904800525904</v>
       </c>
       <c r="G3" t="n">
-        <v>0.411565100315132</v>
+        <v>0.0162197665776192</v>
       </c>
       <c r="H3" t="n">
         <v>-12501.926941861</v>
@@ -3323,16 +3323,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000515696837151099</v>
+        <v>0.0000515661163681425</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000034343594768797</v>
+        <v>0.0000343469282135627</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00515505114745629</v>
+        <v>0.00515374530880925</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00431355338449069</v>
+        <v>0.00431334877773264</v>
       </c>
       <c r="H4" t="n">
         <v>-19664.7423855131</v>
@@ -3352,16 +3352,16 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>501514667358122094644268048</v>
+        <v>0.00005176907828219</v>
       </c>
       <c r="E5" t="n">
-        <v>0.13202578770666</v>
+        <v>0.0000346579025890131</v>
       </c>
       <c r="F5" t="n">
-        <v>1532873946776.21</v>
+        <v>0.00516567219392294</v>
       </c>
       <c r="G5" t="n">
-        <v>0.135543860456709</v>
+        <v>0.00433275138180204</v>
       </c>
       <c r="H5" t="n">
         <v>-19664.7423855131</v>
@@ -3403,23 +3403,37 @@
         <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>33.3333333333333</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>44</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>100</v>
       </c>
     </row>
